--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -119,17 +119,17 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="24.77734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="14.9140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.21875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="18.05859375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="8.6015625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="10.484375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="8.37109375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="5.203125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.05859375" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="34.2890625" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="10.37109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="22.0" customWidth="true"/>
+    <col min="2" max="2" width="22.0" customWidth="true"/>
+    <col min="3" max="3" width="22.0" customWidth="true"/>
+    <col min="4" max="4" width="22.0" customWidth="true"/>
+    <col min="5" max="5" width="22.0" customWidth="true"/>
+    <col min="6" max="6" width="22.0" customWidth="true"/>
+    <col min="7" max="7" width="22.0" customWidth="true"/>
+    <col min="8" max="8" width="22.0" customWidth="true"/>
+    <col min="9" max="9" width="22.0" customWidth="true"/>
+    <col min="10" max="10" width="22.0" customWidth="true"/>
+    <col min="11" max="11" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,29 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+  <si>
+    <t>nombre y apellido</t>
+  </si>
+  <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
   <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -44,34 +47,97 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
-  </si>
-  <si>
-    <t>matias.benitez93@gmail.com</t>
-  </si>
-  <si>
-    <t>+5491169531298</t>
-  </si>
-  <si>
-    <t>2026-05-28T18:30</t>
-  </si>
-  <si>
-    <t>interior</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Maria Lopez</t>
+  </si>
+  <si>
+    <t>2026-05-28T22:15:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>011 3654 9874</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>PENDIENTE</t>
-  </si>
-  <si>
-    <t>Jueves 28 de Mayo de 2026 a las 18:30 hs</t>
-  </si>
-  <si>
-    <t>Villa Crespo</t>
+    <t>matiasg1988@gmail.com</t>
+  </si>
+  <si>
+    <t>Jueves 28 de Mayo de 2026 a las 22:15 hs</t>
+  </si>
+  <si>
+    <t>Julia Medendez</t>
+  </si>
+  <si>
+    <t>2026-05-28T23:00:00</t>
+  </si>
+  <si>
+    <t>01165987845</t>
+  </si>
+  <si>
+    <t>Jueves 28 de Mayo de 2026 a las 23:00 hs</t>
+  </si>
+  <si>
+    <t>Julia Martinez</t>
+  </si>
+  <si>
+    <t>2026-05-28T13:00:00</t>
+  </si>
+  <si>
+    <t>011 50654578</t>
+  </si>
+  <si>
+    <t>Jueves 28 de Mayo de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Nicolás Cabré</t>
+  </si>
+  <si>
+    <t>2026-05-28T20:00:00</t>
+  </si>
+  <si>
+    <t>01165987852</t>
+  </si>
+  <si>
+    <t>Jueves 28 de Mayo de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Promo jueves ($50.000 + servicio, incluye bebida). Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Nicolás Sánchez</t>
+  </si>
+  <si>
+    <t>2026-05-28T22:00:00</t>
+  </si>
+  <si>
+    <t>A criterio del restaurante</t>
+  </si>
+  <si>
+    <t>011 5046 9578</t>
+  </si>
+  <si>
+    <t>Jueves 28 de Mayo de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>Julio Arcaza</t>
+  </si>
+  <si>
+    <t>01152469587</t>
   </si>
 </sst>
 </file>
@@ -116,7 +182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -130,6 +196,10 @@
     <col min="9" max="9" width="22.0" customWidth="true"/>
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
+    <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -166,40 +236,194 @@
       <c r="K1" t="s" s="0">
         <v>10</v>
       </c>
+      <c r="L1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="D2" t="n" s="0">
-        <v>2.0</v>
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="J2" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s" s="0">
-        <v>19</v>
+      <c r="E3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,85 +59,49 @@
     <t>monto_sena</t>
   </si>
   <si>
-    <t>Maria Lopez</t>
-  </si>
-  <si>
-    <t>2026-05-28T22:15:00</t>
+    <t>Laura Briguori</t>
+  </si>
+  <si>
+    <t>2026-05-30T21:30:00</t>
   </si>
   <si>
     <t>Salón Principal</t>
   </si>
   <si>
-    <t>011 3654 9874</t>
+    <t>1136912895</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
+    <t>Laurav.briguori@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 30 de Mayo de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>Matías García</t>
+  </si>
+  <si>
+    <t>2026-05-30T20:30:00</t>
+  </si>
+  <si>
+    <t>01150465015</t>
+  </si>
+  <si>
     <t>matiasg1988@gmail.com</t>
   </si>
   <si>
-    <t>Jueves 28 de Mayo de 2026 a las 22:15 hs</t>
-  </si>
-  <si>
-    <t>Julia Medendez</t>
-  </si>
-  <si>
-    <t>2026-05-28T23:00:00</t>
-  </si>
-  <si>
-    <t>01165987845</t>
-  </si>
-  <si>
-    <t>Jueves 28 de Mayo de 2026 a las 23:00 hs</t>
-  </si>
-  <si>
-    <t>Julia Martinez</t>
-  </si>
-  <si>
-    <t>2026-05-28T13:00:00</t>
-  </si>
-  <si>
-    <t>011 50654578</t>
-  </si>
-  <si>
-    <t>Jueves 28 de Mayo de 2026 a las 13:00 hs</t>
-  </si>
-  <si>
-    <t>Nicolás Cabré</t>
-  </si>
-  <si>
-    <t>2026-05-28T20:00:00</t>
-  </si>
-  <si>
-    <t>01165987852</t>
-  </si>
-  <si>
-    <t>Jueves 28 de Mayo de 2026 a las 20:00 hs</t>
-  </si>
-  <si>
-    <t>Promo jueves ($50.000 + servicio, incluye bebida). Sin restricciones alimentarias.</t>
-  </si>
-  <si>
-    <t>Nicolás Sánchez</t>
-  </si>
-  <si>
-    <t>2026-05-28T22:00:00</t>
-  </si>
-  <si>
-    <t>A criterio del restaurante</t>
-  </si>
-  <si>
-    <t>011 5046 9578</t>
-  </si>
-  <si>
-    <t>Jueves 28 de Mayo de 2026 a las 22:00 hs</t>
-  </si>
-  <si>
-    <t>Julio Arcaza</t>
-  </si>
-  <si>
-    <t>01152469587</t>
+    <t>Sábado 30 de Mayo de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Lucas Perello</t>
+  </si>
+  <si>
+    <t>01154869877</t>
+  </si>
+  <si>
+    <t>Viernes 30 de Mayo de 2026 a las 20:30 hs</t>
   </si>
 </sst>
 </file>
@@ -182,7 +146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -257,7 +221,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -286,7 +250,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>17</v>
@@ -301,21 +265,21 @@
         <v>19</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>17</v>
@@ -330,100 +294,10 @@
         <v>19</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s" s="0">
         <v>29</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="C5" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="K5" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="M5" t="s" s="0">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="C6" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="K6" t="s" s="0">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="C7" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="K7" t="s" s="0">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -58,51 +58,6 @@
   <si>
     <t>monto_sena</t>
   </si>
-  <si>
-    <t>Laura Briguori</t>
-  </si>
-  <si>
-    <t>2026-05-30T21:30:00</t>
-  </si>
-  <si>
-    <t>Salón Principal</t>
-  </si>
-  <si>
-    <t>1136912895</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Laurav.briguori@gmail.com</t>
-  </si>
-  <si>
-    <t>Sábado 30 de Mayo de 2026 a las 21:30 hs</t>
-  </si>
-  <si>
-    <t>Matías García</t>
-  </si>
-  <si>
-    <t>2026-05-30T20:30:00</t>
-  </si>
-  <si>
-    <t>01150465015</t>
-  </si>
-  <si>
-    <t>matiasg1988@gmail.com</t>
-  </si>
-  <si>
-    <t>Sábado 30 de Mayo de 2026 a las 20:30 hs</t>
-  </si>
-  <si>
-    <t>Lucas Perello</t>
-  </si>
-  <si>
-    <t>01154869877</t>
-  </si>
-  <si>
-    <t>Viernes 30 de Mayo de 2026 a las 20:30 hs</t>
-  </si>
 </sst>
 </file>
 
@@ -146,7 +101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -213,93 +168,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="K3" t="s" s="0">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="K4" t="s" s="0">
-        <v>29</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -57,6 +57,27 @@
   </si>
   <si>
     <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexis Alarcón</t>
+  </si>
+  <si>
+    <t>2026-06-02T19:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+56979900412</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alexis_alarcon_a@yahoo.es</t>
+  </si>
+  <si>
+    <t>Martes 2 de Junio de 2026 a las 19:30 hs</t>
   </si>
 </sst>
 </file>
@@ -101,7 +122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -168,6 +189,35 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>alexis_alarcon_a@yahoo.es</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
   </si>
   <si>
     <t>Martes 2 de Junio de 2026 a las 19:30 hs</t>
@@ -214,8 +217,11 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
       <c r="K2" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,28 +59,34 @@
     <t>monto_sena</t>
   </si>
   <si>
-    <t>Alexis Alarcón</t>
-  </si>
-  <si>
-    <t>2026-06-02T19:30:00</t>
+    <t>Christopher León Cáceres</t>
+  </si>
+  <si>
+    <t>2026-06-03T17:15:00</t>
   </si>
   <si>
     <t>Salón Principal</t>
   </si>
   <si>
-    <t>+56979900412</t>
+    <t>+51 977154378</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>alexis_alarcon_a@yahoo.es</t>
+    <t>christleon240@gmail.com</t>
   </si>
   <si>
     <t>CONFIRMADA</t>
   </si>
   <si>
-    <t>Martes 2 de Junio de 2026 a las 19:30 hs</t>
+    <t>Miércoles 03 de Junio de 2026 a las 17:15 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Aniversario. Sin restricciones alimentarias.</t>
   </si>
 </sst>
 </file>
@@ -200,7 +206,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -222,6 +228,12 @@
       </c>
       <c r="K2" t="s" s="0">
         <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -77,7 +77,7 @@
     <t>christleon240@gmail.com</t>
   </si>
   <si>
-    <t>CONFIRMADA</t>
+    <t>TERMINADA</t>
   </si>
   <si>
     <t>Miércoles 03 de Junio de 2026 a las 17:15 hs</t>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,6 +59,33 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t xml:space="preserve">Andres </t>
+  </si>
+  <si>
+    <t>2026-06-03T22:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1130184412</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Vipkingproducciones@gmail</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
     <t>Christopher León Cáceres</t>
   </si>
   <si>
@@ -69,9 +96,6 @@
   </si>
   <si>
     <t>+51 977154378</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>christleon240@gmail.com</t>
@@ -131,7 +155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -206,7 +230,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -223,17 +247,55 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
       <c r="J2" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s" s="0">
         <v>22</v>
       </c>
       <c r="L2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
         <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -230,7 +230,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -80,7 +80,7 @@
     <t>M9</t>
   </si>
   <si>
-    <t>CONFIRMADA</t>
+    <t>TERMINADA</t>
   </si>
   <si>
     <t>cumpleaños</t>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>christleon240@gmail.com</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
   </si>
   <si>
     <t>Miércoles 03 de Junio de 2026 a las 17:15 hs</t>
@@ -286,16 +283,16 @@
         <v>28</v>
       </c>
       <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="K3" t="s" s="0">
+      <c r="L3" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="M3" t="s" s="0">
         <v>31</v>
-      </c>
-      <c r="M3" t="s" s="0">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,55 +59,58 @@
     <t>monto_sena</t>
   </si>
   <si>
-    <t xml:space="preserve">Andres </t>
-  </si>
-  <si>
-    <t>2026-06-03T22:00</t>
+    <t>Rocío Liptzis</t>
+  </si>
+  <si>
+    <t>2026-06-04T21:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1139200650</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>rocio.liptzis@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Jueves 4 de junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Rocío. Incluye 1 niña de 7 años (medio cubierto). Torta simbólica de cortesía, copa de champagne para brindar. Cumpleañera no paga menú, solo servicio de mesa ($4.000) + bebidas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabiana Paso </t>
+  </si>
+  <si>
+    <t>2026-06-04T20:30</t>
   </si>
   <si>
     <t>Salón</t>
   </si>
   <si>
-    <t>1130184412</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Vipkingproducciones@gmail</t>
-  </si>
-  <si>
-    <t>M9</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
-  </si>
-  <si>
-    <t>cumpleaños</t>
-  </si>
-  <si>
-    <t>Christopher León Cáceres</t>
-  </si>
-  <si>
-    <t>2026-06-03T17:15:00</t>
-  </si>
-  <si>
-    <t>Salón Principal</t>
-  </si>
-  <si>
-    <t>+51 977154378</t>
-  </si>
-  <si>
-    <t>christleon240@gmail.com</t>
-  </si>
-  <si>
-    <t>Miércoles 03 de Junio de 2026 a las 17:15 hs</t>
-  </si>
-  <si>
-    <t>aniversario</t>
-  </si>
-  <si>
-    <t>Aniversario. Sin restricciones alimentarias.</t>
+    <t>11983843743</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanesa </t>
+  </si>
+  <si>
+    <t>2026-06-04T21:00</t>
+  </si>
+  <si>
+    <t>1160075286</t>
   </si>
 </sst>
 </file>
@@ -152,7 +155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -227,7 +230,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -244,55 +247,84 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="J2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="K2" t="s" s="0">
         <v>22</v>
       </c>
       <c r="L2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="N2" t="s" s="0">
-        <v>19</v>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="J3" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s" s="0">
+      <c r="E4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="L3" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s" s="0">
-        <v>31</v>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -77,7 +77,7 @@
     <t>rocio.liptzis@gmail.com</t>
   </si>
   <si>
-    <t>CONFIRMADA</t>
+    <t>TERMINADA</t>
   </si>
   <si>
     <t>Jueves 4 de junio de 2026 a las 21:00 hs</t>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="44">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,58 +59,91 @@
     <t>monto_sena</t>
   </si>
   <si>
-    <t>Rocío Liptzis</t>
-  </si>
-  <si>
-    <t>2026-06-04T21:00:00</t>
+    <t>Cristian Acosta</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:30:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1140917131</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>cristianacostaaa2002@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 5 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita romántica. Sector asignado: Siberia (cliente pidió lo más tranquilo e íntimo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alegre Lilen </t>
+  </si>
+  <si>
+    <t>2026-06-05T21:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1126630385</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodriguez Yesica </t>
+  </si>
+  <si>
+    <t>92804181959</t>
+  </si>
+  <si>
+    <t>seña 610</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Andrea Pulido</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:30</t>
+  </si>
+  <si>
+    <t>1162322025</t>
+  </si>
+  <si>
+    <t>Selena García</t>
   </si>
   <si>
     <t>Salón Principal</t>
   </si>
   <si>
-    <t>1139200650</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>rocio.liptzis@gmail.com</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
-  </si>
-  <si>
-    <t>Jueves 4 de junio de 2026 a las 21:00 hs</t>
+    <t>1140872576</t>
+  </si>
+  <si>
+    <t>seleegarciaa93@gmail.com</t>
   </si>
   <si>
     <t>cumpleaños</t>
   </si>
   <si>
-    <t>Cumpleaños de Rocío. Incluye 1 niña de 7 años (medio cubierto). Torta simbólica de cortesía, copa de champagne para brindar. Cumpleañera no paga menú, solo servicio de mesa ($4.000) + bebidas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabiana Paso </t>
-  </si>
-  <si>
-    <t>2026-06-04T20:30</t>
-  </si>
-  <si>
-    <t>Salón</t>
-  </si>
-  <si>
-    <t>11983843743</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanesa </t>
-  </si>
-  <si>
-    <t>2026-06-04T21:00</t>
-  </si>
-  <si>
-    <t>1160075286</t>
+    <t>Cumpleaños del novio. Incluye torta simbólica, copa de champagne de cortesía. El cumpleañero no paga menú, solo servicio de mesa ($4.000) + bebidas.</t>
   </si>
 </sst>
 </file>
@@ -155,7 +188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -230,7 +263,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -247,46 +280,46 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="K2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="L2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="M2" t="s" s="0">
         <v>23</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="C3" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="D3" t="s" s="0">
+      <c r="E3" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
+      <c r="J3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="J3" t="s" s="0">
-        <v>21</v>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>19</v>
@@ -294,16 +327,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>32</v>
@@ -315,16 +348,95 @@
         <v>19</v>
       </c>
       <c r="H4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="J4" t="s" s="0">
+      <c r="L4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>199998.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K6" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="L4" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="N4" t="s" s="0">
-        <v>19</v>
+      <c r="L6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>cristianacostaaa2002@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
   </si>
   <si>
     <t>Viernes 5 de Junio de 2026 a las 21:30 hs</t>
@@ -280,31 +283,34 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
       <c r="K2" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>19</v>
@@ -313,13 +319,13 @@
         <v>19</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>19</v>
@@ -327,19 +333,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>20.0</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>19</v>
@@ -348,19 +354,19 @@
         <v>19</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" t="n" s="0">
         <v>199998.0</v>
@@ -368,19 +374,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -389,13 +395,13 @@
         <v>19</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N5" t="s" s="0">
         <v>19</v>
@@ -403,7 +409,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>16</v>
@@ -412,10 +418,10 @@
         <v>2.0</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>19</v>
@@ -424,19 +430,19 @@
         <v>19</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="44">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -77,7 +77,7 @@
     <t>cristianacostaaa2002@gmail.com</t>
   </si>
   <si>
-    <t>CANCELADA</t>
+    <t>CONFIRMADA</t>
   </si>
   <si>
     <t>Viernes 5 de Junio de 2026 a las 21:30 hs</t>
@@ -102,9 +102,6 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
   </si>
   <si>
     <t>otra</t>
@@ -322,10 +319,10 @@
         <v>29</v>
       </c>
       <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s" s="0">
         <v>30</v>
-      </c>
-      <c r="L3" t="s" s="0">
-        <v>31</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>19</v>
@@ -333,7 +330,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="0">
         <v>26</v>
@@ -345,7 +342,7 @@
         <v>27</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>19</v>
@@ -357,16 +354,16 @@
         <v>29</v>
       </c>
       <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="L4" t="s" s="0">
-        <v>31</v>
-      </c>
       <c r="M4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="N4" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="N4" t="s" s="0">
-        <v>35</v>
       </c>
       <c r="O4" t="n" s="0">
         <v>199998.0</v>
@@ -374,10 +371,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>36</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>37</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>5.0</v>
@@ -386,7 +383,7 @@
         <v>27</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -398,10 +395,10 @@
         <v>29</v>
       </c>
       <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
         <v>30</v>
-      </c>
-      <c r="L5" t="s" s="0">
-        <v>31</v>
       </c>
       <c r="N5" t="s" s="0">
         <v>19</v>
@@ -409,7 +406,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="0">
         <v>16</v>
@@ -418,31 +415,31 @@
         <v>2.0</v>
       </c>
       <c r="D6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="E6" t="s" s="0">
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="F6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>42</v>
-      </c>
       <c r="J6" t="s" s="0">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s" s="0">
         <v>22</v>
       </c>
       <c r="L6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="M6" t="s" s="0">
         <v>43</v>
-      </c>
-      <c r="M6" t="s" s="0">
-        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,28 +59,46 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>Tomás Leska</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:30:00</t>
+  </si>
+  <si>
+    <t>Puerto Madero</t>
+  </si>
+  <si>
+    <t>1124037090</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tomasleska07@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 5 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Aniversario de la pareja del cliente.</t>
+  </si>
+  <si>
     <t>Cristian Acosta</t>
   </si>
   <si>
-    <t>2026-06-05T21:30:00</t>
-  </si>
-  <si>
     <t>Siberia</t>
   </si>
   <si>
     <t>1140917131</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>cristianacostaaa2002@gmail.com</t>
   </si>
   <si>
     <t>CONFIRMADA</t>
-  </si>
-  <si>
-    <t>Viernes 5 de Junio de 2026 a las 21:30 hs</t>
   </si>
   <si>
     <t>cita</t>
@@ -188,7 +206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -280,52 +298,52 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="K2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="L2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="M2" t="s" s="0">
         <v>23</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="E3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="C3" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="D3" t="s" s="0">
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="J3" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
+      <c r="K3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="J3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="L3" t="s" s="0">
+      <c r="M3" t="s" s="0">
         <v>30</v>
-      </c>
-      <c r="N3" t="s" s="0">
-        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -333,16 +351,16 @@
         <v>31</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>19</v>
@@ -351,95 +369,130 @@
         <v>19</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="M4" t="s" s="0">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="O4" t="n" s="0">
-        <v>199998.0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="J5" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="C5" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="L5" t="s" s="0">
-        <v>30</v>
+      <c r="M5" t="s" s="0">
+        <v>39</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>19</v>
+        <v>40</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>199998.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="C6" t="n" s="0">
+      <c r="C7" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="D6" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="J6" t="s" s="0">
+      <c r="D7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="K7" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K6" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="L6" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="M6" t="s" s="0">
-        <v>43</v>
+      <c r="L7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
   </si>
   <si>
     <t>otra</t>
@@ -372,10 +375,10 @@
         <v>35</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N4" t="s" s="0">
         <v>19</v>
@@ -383,7 +386,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>32</v>
@@ -395,7 +398,7 @@
         <v>33</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -410,13 +413,13 @@
         <v>28</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O5" t="n" s="0">
         <v>199998.0</v>
@@ -424,10 +427,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>5.0</v>
@@ -436,7 +439,7 @@
         <v>33</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>19</v>
@@ -451,7 +454,7 @@
         <v>28</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N6" t="s" s="0">
         <v>19</v>
@@ -459,7 +462,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s" s="0">
         <v>16</v>
@@ -468,10 +471,10 @@
         <v>2.0</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>19</v>
@@ -480,7 +483,7 @@
         <v>19</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>28</v>
@@ -489,10 +492,10 @@
         <v>21</v>
       </c>
       <c r="L7" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M7" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="51">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -77,6 +77,9 @@
     <t>tomasleska07@gmail.com</t>
   </si>
   <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
     <t>Viernes 5 de Junio de 2026 a las 21:30 hs</t>
   </si>
   <si>
@@ -98,55 +101,52 @@
     <t>cristianacostaaa2002@gmail.com</t>
   </si>
   <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita romántica. Sector asignado: Siberia (cliente pidió lo más tranquilo e íntimo).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alegre Lilen </t>
+  </si>
+  <si>
+    <t>2026-06-05T21:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1126630385</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rodriguez Yesica </t>
+  </si>
+  <si>
+    <t>92804181959</t>
+  </si>
+  <si>
+    <t>seña 610</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Andrea Pulido</t>
+  </si>
+  <si>
+    <t>2026-06-05T21:30</t>
+  </si>
+  <si>
+    <t>1162322025</t>
+  </si>
+  <si>
     <t>CONFIRMADA</t>
-  </si>
-  <si>
-    <t>cita</t>
-  </si>
-  <si>
-    <t>Cita romántica. Sector asignado: Siberia (cliente pidió lo más tranquilo e íntimo).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alegre Lilen </t>
-  </si>
-  <si>
-    <t>2026-06-05T21:00</t>
-  </si>
-  <si>
-    <t>Salón</t>
-  </si>
-  <si>
-    <t>1126630385</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
-  </si>
-  <si>
-    <t>otra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rodriguez Yesica </t>
-  </si>
-  <si>
-    <t>92804181959</t>
-  </si>
-  <si>
-    <t>seña 610</t>
-  </si>
-  <si>
-    <t>Sí</t>
-  </si>
-  <si>
-    <t>Andrea Pulido</t>
-  </si>
-  <si>
-    <t>2026-06-05T21:30</t>
-  </si>
-  <si>
-    <t>1162322025</t>
   </si>
   <si>
     <t>Selena García</t>
@@ -301,19 +301,22 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
       <c r="K2" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s" s="0">
         <v>16</v>
@@ -322,10 +325,10 @@
         <v>2.0</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>19</v>
@@ -334,13 +337,13 @@
         <v>19</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" t="s" s="0">
         <v>29</v>
@@ -375,10 +378,10 @@
         <v>35</v>
       </c>
       <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s" s="0">
         <v>36</v>
-      </c>
-      <c r="L4" t="s" s="0">
-        <v>37</v>
       </c>
       <c r="N4" t="s" s="0">
         <v>19</v>
@@ -386,7 +389,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>32</v>
@@ -398,7 +401,7 @@
         <v>33</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -410,16 +413,16 @@
         <v>35</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s" s="0">
         <v>40</v>
-      </c>
-      <c r="N5" t="s" s="0">
-        <v>41</v>
       </c>
       <c r="O5" t="n" s="0">
         <v>199998.0</v>
@@ -427,10 +430,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="0">
         <v>42</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>43</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>5.0</v>
@@ -439,7 +442,7 @@
         <v>33</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>19</v>
@@ -451,10 +454,10 @@
         <v>35</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N6" t="s" s="0">
         <v>19</v>
@@ -486,10 +489,10 @@
         <v>48</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L7" t="s" s="0">
         <v>49</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -489,7 +489,7 @@
         <v>48</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s" s="0">
         <v>22</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,112 +59,133 @@
     <t>monto_sena</t>
   </si>
   <si>
-    <t>Tomás Leska</t>
-  </si>
-  <si>
-    <t>2026-06-05T21:30:00</t>
-  </si>
-  <si>
-    <t>Puerto Madero</t>
-  </si>
-  <si>
-    <t>1124037090</t>
+    <t>Toledo melodi</t>
+  </si>
+  <si>
+    <t>2026-06-06T19:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1154833127</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>tomasleska07@gmail.com</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
-  </si>
-  <si>
-    <t>Viernes 5 de Junio de 2026 a las 21:30 hs</t>
-  </si>
-  <si>
-    <t>aniversario</t>
-  </si>
-  <si>
-    <t>Aniversario de la pareja del cliente.</t>
-  </si>
-  <si>
-    <t>Cristian Acosta</t>
-  </si>
-  <si>
-    <t>Siberia</t>
-  </si>
-  <si>
-    <t>1140917131</t>
-  </si>
-  <si>
-    <t>cristianacostaaa2002@gmail.com</t>
-  </si>
-  <si>
-    <t>cita</t>
-  </si>
-  <si>
-    <t>Cita romántica. Sector asignado: Siberia (cliente pidió lo más tranquilo e íntimo).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alegre Lilen </t>
-  </si>
-  <si>
-    <t>2026-06-05T21:00</t>
-  </si>
-  <si>
-    <t>Salón</t>
-  </si>
-  <si>
-    <t>1126630385</t>
+    <t>Luisgabrieltoledozanhaoria@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Martina Fernández</t>
+  </si>
+  <si>
+    <t>2026-06-06T20:30:00</t>
+  </si>
+  <si>
+    <t>Preferencia: cerca de las islas de comida</t>
+  </si>
+  <si>
+    <t>1167546734</t>
+  </si>
+  <si>
+    <t>martinafernandez0000@outlook.es</t>
+  </si>
+  <si>
+    <t>Sábado 6 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t>Una semana antes del cumpleaños de Martina. Cliente prefiere ubicación cerca de las islas de comida.</t>
+  </si>
+  <si>
+    <t>Lilian Sacharuk</t>
+  </si>
+  <si>
+    <t>2026-06-06T13:45:00</t>
+  </si>
+  <si>
+    <t>Junto al ventanal</t>
+  </si>
+  <si>
+    <t>11 5604 0662</t>
+  </si>
+  <si>
+    <t>altoalcance@fibertel.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 6 de Junio de 2026 a las 13:45 hs</t>
+  </si>
+  <si>
+    <t>Cliente prefiere vista al río, junto al ventanal, tranquilo — confirmar disponibilidad en local (sábado, sin asignación de sector).</t>
+  </si>
+  <si>
+    <t>Alejandro Mesler</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1149376959</t>
+  </si>
+  <si>
+    <t>halejandro666@hotmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 06 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños en el grupo. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Nocetti miriam</t>
+  </si>
+  <si>
+    <t>2026-06-06T20:30</t>
+  </si>
+  <si>
+    <t>2215360392</t>
+  </si>
+  <si>
+    <t>miriamnocetti@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>mirianrosetri@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 sra vegana </t>
+  </si>
+  <si>
+    <t>YAGO</t>
+  </si>
+  <si>
+    <t>2026-06-06T21:00</t>
+  </si>
+  <si>
+    <t>1141746833</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>otra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rodriguez Yesica </t>
-  </si>
-  <si>
-    <t>92804181959</t>
-  </si>
-  <si>
-    <t>seña 610</t>
-  </si>
-  <si>
-    <t>Sí</t>
-  </si>
-  <si>
-    <t>Andrea Pulido</t>
-  </si>
-  <si>
-    <t>2026-06-05T21:30</t>
-  </si>
-  <si>
-    <t>1162322025</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
-  </si>
-  <si>
-    <t>Selena García</t>
-  </si>
-  <si>
-    <t>Salón Principal</t>
-  </si>
-  <si>
-    <t>1140872576</t>
-  </si>
-  <si>
-    <t>seleegarciaa93@gmail.com</t>
-  </si>
-  <si>
-    <t>cumpleaños</t>
-  </si>
-  <si>
-    <t>Cumpleaños del novio. Incluye torta simbólica, copa de champagne de cortesía. El cumpleañero no paga menú, solo servicio de mesa ($4.000) + bebidas.</t>
+    <t>Flores Ariana</t>
+  </si>
+  <si>
+    <t>2026-06-06T20:00</t>
+  </si>
+  <si>
+    <t>1123303473</t>
   </si>
 </sst>
 </file>
@@ -209,7 +230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -284,7 +305,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -304,46 +325,43 @@
       <c r="J2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="L2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="L2" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>24</v>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="D3" t="s" s="0">
+      <c r="E3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>27</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>28</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="L3" t="s" s="0">
         <v>29</v>
@@ -360,7 +378,7 @@
         <v>32</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>33</v>
@@ -380,28 +398,28 @@
       <c r="J4" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="L4" t="s" s="0">
+      <c r="K4" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="N4" t="s" s="0">
-        <v>19</v>
+      <c r="M4" t="s" s="0">
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -410,39 +428,36 @@
         <v>19</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>21</v>
       </c>
+      <c r="K5" t="s" s="0">
+        <v>42</v>
+      </c>
       <c r="L5" t="s" s="0">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="N5" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="O5" t="n" s="0">
-        <v>199998.0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>5.0</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>19</v>
@@ -451,13 +466,19 @@
         <v>19</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>49</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>36</v>
+        <v>22</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>50</v>
       </c>
       <c r="N6" t="s" s="0">
         <v>19</v>
@@ -465,19 +486,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>19</v>
@@ -486,19 +507,51 @@
         <v>19</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K7" t="s" s="0">
-        <v>22</v>
-      </c>
       <c r="L7" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="M7" t="s" s="0">
-        <v>50</v>
+        <v>29</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="59">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>altoalcance@fibertel.com.ar</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
   </si>
   <si>
     <t>Sábado 6 de Junio de 2026 a las 13:45 hs</t>
@@ -396,18 +399,18 @@
         <v>35</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>24</v>
@@ -416,10 +419,10 @@
         <v>6.0</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -428,27 +431,27 @@
         <v>19</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>22</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>5.0</v>
@@ -457,7 +460,7 @@
         <v>17</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>19</v>
@@ -466,19 +469,19 @@
         <v>19</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L6" t="s" s="0">
         <v>22</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N6" t="s" s="0">
         <v>19</v>
@@ -486,10 +489,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>8.0</v>
@@ -498,7 +501,7 @@
         <v>17</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>19</v>
@@ -507,7 +510,7 @@
         <v>19</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J7" t="s" s="0">
         <v>21</v>
@@ -521,10 +524,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>6.0</v>
@@ -533,7 +536,7 @@
         <v>17</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s" s="0">
         <v>19</v>
@@ -542,7 +545,7 @@
         <v>19</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J8" t="s" s="0">
         <v>21</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,25 +59,55 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>Miguel Rojas</t>
+  </si>
+  <si>
+    <t>2026-06-06T22:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>2215712486</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>viroxmi61@hotmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Christian Masia</t>
+  </si>
+  <si>
+    <t>2026-06-06T21:30</t>
+  </si>
+  <si>
+    <t>1126442554</t>
+  </si>
+  <si>
+    <t>christianmasia1992@gmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
     <t>Toledo melodi</t>
   </si>
   <si>
     <t>2026-06-06T19:00</t>
   </si>
   <si>
-    <t>Salón</t>
-  </si>
-  <si>
     <t>1154833127</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Luisgabrieltoledozanhaoria@gmail.com</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
   </si>
   <si>
     <t>cumpleaños</t>
@@ -233,7 +263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -308,7 +338,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -325,10 +355,10 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
       <c r="J2" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="L2" t="s" s="0">
         <v>22</v>
       </c>
       <c r="N2" t="s" s="0">
@@ -343,217 +373,287 @@
         <v>24</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
+      <c r="I3" t="s" s="0">
         <v>27</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="L3" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s" s="0">
-        <v>30</v>
+        <v>22</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="J4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C4" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="J4" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="K4" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="M4" t="s" s="0">
-        <v>38</v>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L5" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>24</v>
-      </c>
-      <c r="C5" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="D5" t="s" s="0">
+      <c r="M5" t="s" s="0">
         <v>40</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K5" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="L5" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="M5" t="s" s="0">
-        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="J6" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="C6" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s" s="0">
+      <c r="K6" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="F6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s" s="0">
+      <c r="M6" t="s" s="0">
         <v>48</v>
-      </c>
-      <c r="J6" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K6" t="s" s="0">
-        <v>50</v>
-      </c>
-      <c r="L6" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="M6" t="s" s="0">
-        <v>51</v>
-      </c>
-      <c r="N6" t="s" s="0">
-        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="J7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K7" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="C7" t="n" s="0">
-        <v>8.0</v>
-      </c>
-      <c r="D7" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s" s="0">
+      <c r="L7" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="M7" t="s" s="0">
         <v>54</v>
-      </c>
-      <c r="F7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s" s="0">
-        <v>55</v>
-      </c>
-      <c r="J7" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="L7" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="N7" t="s" s="0">
-        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B8" t="s" s="0">
-        <v>57</v>
-      </c>
       <c r="C8" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="D8" t="s" s="0">
         <v>17</v>
       </c>
       <c r="E8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="F8" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s" s="0">
-        <v>55</v>
-      </c>
       <c r="J8" t="s" s="0">
-        <v>21</v>
+        <v>59</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>60</v>
       </c>
       <c r="L8" t="s" s="0">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>61</v>
       </c>
       <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="N10" t="s" s="0">
         <v>19</v>
       </c>
     </row>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="72">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,30 +59,42 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>LITO(JUAN PABLO)</t>
+  </si>
+  <si>
+    <t>2026-06-06T21:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1139262072</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>brasasargentinas.reservas@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
     <t>Miguel Rojas</t>
   </si>
   <si>
     <t>2026-06-06T22:00</t>
   </si>
   <si>
-    <t>Salón</t>
-  </si>
-  <si>
     <t>2215712486</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>viroxmi61@hotmail.com</t>
   </si>
   <si>
     <t>M4</t>
   </si>
   <si>
-    <t>CONFIRMADA</t>
-  </si>
-  <si>
     <t>Christian Masia</t>
   </si>
   <si>
@@ -201,9 +213,6 @@
   </si>
   <si>
     <t>YAGO</t>
-  </si>
-  <si>
-    <t>2026-06-06T21:00</t>
   </si>
   <si>
     <t>1141746833</t>
@@ -263,7 +272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -338,7 +347,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -355,11 +364,8 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="J2" t="s" s="0">
         <v>21</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>22</v>
       </c>
       <c r="N2" t="s" s="0">
         <v>19</v>
@@ -367,34 +373,34 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>24</v>
-      </c>
       <c r="C3" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>17</v>
       </c>
       <c r="E3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
+      <c r="I3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="I3" t="s" s="0">
-        <v>27</v>
-      </c>
       <c r="J3" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>19</v>
@@ -402,34 +408,34 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>29</v>
-      </c>
       <c r="C4" t="n" s="0">
-        <v>7.0</v>
+        <v>2.0</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>17</v>
       </c>
       <c r="E4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="F4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s" s="0">
+      <c r="I4" t="s" s="0">
         <v>31</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="L4" t="s" s="0">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="N4" t="s" s="0">
         <v>19</v>
@@ -437,186 +443,186 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="C5" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="C5" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="D5" t="s" s="0">
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="E5" t="s" s="0">
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="F5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="K5" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="L5" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="M5" t="s" s="0">
-        <v>40</v>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="C6" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="D6" t="s" s="0">
+      <c r="L6" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="E6" t="s" s="0">
+      <c r="M6" t="s" s="0">
         <v>44</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="J6" t="s" s="0">
-        <v>46</v>
-      </c>
-      <c r="K6" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="M6" t="s" s="0">
-        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="B7" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="C7" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="D7" t="s" s="0">
+      <c r="J7" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="E7" t="s" s="0">
+      <c r="K7" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="F7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s" s="0">
+      <c r="M7" t="s" s="0">
         <v>52</v>
-      </c>
-      <c r="J7" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="K7" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="L7" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="M7" t="s" s="0">
-        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="C8" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="D8" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s" s="0">
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="F8" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s" s="0">
+      <c r="L8" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M8" t="s" s="0">
         <v>58</v>
-      </c>
-      <c r="J8" t="s" s="0">
-        <v>59</v>
-      </c>
-      <c r="K8" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="L8" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="M8" t="s" s="0">
-        <v>61</v>
-      </c>
-      <c r="N8" t="s" s="0">
-        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="D9" t="s" s="0">
         <v>17</v>
       </c>
       <c r="E9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="K9" t="s" s="0">
         <v>64</v>
       </c>
-      <c r="F9" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H9" t="s" s="0">
+      <c r="L9" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s" s="0">
         <v>65</v>
-      </c>
-      <c r="J9" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="L9" t="s" s="0">
-        <v>39</v>
       </c>
       <c r="N9" t="s" s="0">
         <v>19</v>
@@ -627,33 +633,68 @@
         <v>66</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="D10" t="s" s="0">
         <v>17</v>
       </c>
       <c r="E10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="F10" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s" s="0">
-        <v>65</v>
-      </c>
       <c r="J10" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L10" t="s" s="0">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="N11" t="s" s="0">
         <v>19</v>
       </c>
     </row>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -689,7 +689,7 @@
         <v>68</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="L11" t="s" s="0">
         <v>43</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -575,7 +575,7 @@
         <v>56</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="K8" t="s" s="0">
         <v>57</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -122,6 +122,9 @@
     <t>Luisgabrieltoledozanhaoria@gmail.com</t>
   </si>
   <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
     <t>cumpleaños</t>
   </si>
   <si>
@@ -201,9 +204,6 @@
   </si>
   <si>
     <t>miriamnocetti@gmail.com</t>
-  </si>
-  <si>
-    <t>CANCELADA</t>
   </si>
   <si>
     <t>mirianrosetri@gmail.com</t>
@@ -467,10 +467,10 @@
         <v>35</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N5" t="s" s="0">
         <v>19</v>
@@ -478,19 +478,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>19</v>
@@ -499,36 +499,36 @@
         <v>19</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>19</v>
@@ -537,33 +537,33 @@
         <v>19</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K7" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M7" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s" s="0">
         <v>19</v>
@@ -572,27 +572,27 @@
         <v>19</v>
       </c>
       <c r="H8" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K8" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L8" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M8" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>5.0</v>
@@ -601,7 +601,7 @@
         <v>17</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s" s="0">
         <v>19</v>
@@ -610,16 +610,16 @@
         <v>19</v>
       </c>
       <c r="H9" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s" s="0">
         <v>64</v>
       </c>
       <c r="L9" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M9" t="s" s="0">
         <v>65</v>
@@ -657,7 +657,7 @@
         <v>21</v>
       </c>
       <c r="L10" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N10" t="s" s="0">
         <v>19</v>
@@ -689,10 +689,10 @@
         <v>68</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L11" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N11" t="s" s="0">
         <v>19</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -77,24 +77,27 @@
     <t>brasasargentinas.reservas@gmail.com</t>
   </si>
   <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Miguel Rojas</t>
+  </si>
+  <si>
+    <t>2026-06-06T22:00</t>
+  </si>
+  <si>
+    <t>2215712486</t>
+  </si>
+  <si>
+    <t>viroxmi61@hotmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
     <t>CONFIRMADA</t>
   </si>
   <si>
-    <t>Miguel Rojas</t>
-  </si>
-  <si>
-    <t>2026-06-06T22:00</t>
-  </si>
-  <si>
-    <t>2215712486</t>
-  </si>
-  <si>
-    <t>viroxmi61@hotmail.com</t>
-  </si>
-  <si>
-    <t>M4</t>
-  </si>
-  <si>
     <t>Christian Masia</t>
   </si>
   <si>
@@ -120,9 +123,6 @@
   </si>
   <si>
     <t>Luisgabrieltoledozanhaoria@gmail.com</t>
-  </si>
-  <si>
-    <t>CANCELADA</t>
   </si>
   <si>
     <t>cumpleaños</t>
@@ -400,7 +400,7 @@
         <v>26</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>19</v>
@@ -408,10 +408,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>2.0</v>
@@ -420,7 +420,7 @@
         <v>17</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>19</v>
@@ -429,13 +429,13 @@
         <v>19</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N4" t="s" s="0">
         <v>19</v>
@@ -443,10 +443,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>7.0</v>
@@ -455,7 +455,7 @@
         <v>17</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -464,10 +464,10 @@
         <v>19</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>37</v>
@@ -502,7 +502,7 @@
         <v>42</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K6" t="s" s="0">
         <v>43</v>
@@ -613,7 +613,7 @@
         <v>63</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s" s="0">
         <v>64</v>
@@ -654,7 +654,7 @@
         <v>68</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L10" t="s" s="0">
         <v>44</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -113,6 +113,9 @@
     <t>M1</t>
   </si>
   <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
     <t>Toledo melodi</t>
   </si>
   <si>
@@ -165,9 +168,6 @@
   </si>
   <si>
     <t>altoalcance@fibertel.com.ar</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
   </si>
   <si>
     <t>Sábado 6 de Junio de 2026 a las 13:45 hs</t>
@@ -435,7 +435,7 @@
         <v>32</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N4" t="s" s="0">
         <v>19</v>
@@ -443,10 +443,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>7.0</v>
@@ -455,7 +455,7 @@
         <v>17</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -464,13 +464,13 @@
         <v>19</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>21</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N5" t="s" s="0">
         <v>19</v>
@@ -478,19 +478,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s" s="0">
         <v>19</v>
@@ -499,36 +499,36 @@
         <v>19</v>
       </c>
       <c r="H6" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K6" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M6" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s" s="0">
         <v>19</v>
@@ -537,10 +537,10 @@
         <v>19</v>
       </c>
       <c r="H7" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J7" t="s" s="0">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K7" t="s" s="0">
         <v>52</v>
@@ -554,7 +554,7 @@
         <v>54</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>6.0</v>
@@ -575,13 +575,13 @@
         <v>57</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K8" t="s" s="0">
         <v>58</v>
       </c>
       <c r="L8" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M8" t="s" s="0">
         <v>59</v>
@@ -619,7 +619,7 @@
         <v>64</v>
       </c>
       <c r="L9" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M9" t="s" s="0">
         <v>65</v>
@@ -654,10 +654,10 @@
         <v>68</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L10" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N10" t="s" s="0">
         <v>19</v>
@@ -689,10 +689,10 @@
         <v>68</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="L11" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N11" t="s" s="0">
         <v>19</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="71">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -77,55 +77,52 @@
     <t>brasasargentinas.reservas@gmail.com</t>
   </si>
   <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Miguel Rojas</t>
+  </si>
+  <si>
+    <t>2026-06-06T22:00</t>
+  </si>
+  <si>
+    <t>2215712486</t>
+  </si>
+  <si>
+    <t>viroxmi61@hotmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>Christian Masia</t>
+  </si>
+  <si>
+    <t>2026-06-06T21:30</t>
+  </si>
+  <si>
+    <t>1126442554</t>
+  </si>
+  <si>
+    <t>christianmasia1992@gmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>Toledo melodi</t>
+  </si>
+  <si>
+    <t>2026-06-06T19:00</t>
+  </si>
+  <si>
+    <t>1154833127</t>
+  </si>
+  <si>
+    <t>Luisgabrieltoledozanhaoria@gmail.com</t>
+  </si>
+  <si>
     <t>CANCELADA</t>
-  </si>
-  <si>
-    <t>Miguel Rojas</t>
-  </si>
-  <si>
-    <t>2026-06-06T22:00</t>
-  </si>
-  <si>
-    <t>2215712486</t>
-  </si>
-  <si>
-    <t>viroxmi61@hotmail.com</t>
-  </si>
-  <si>
-    <t>M4</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
-  </si>
-  <si>
-    <t>Christian Masia</t>
-  </si>
-  <si>
-    <t>2026-06-06T21:30</t>
-  </si>
-  <si>
-    <t>1126442554</t>
-  </si>
-  <si>
-    <t>christianmasia1992@gmail.com</t>
-  </si>
-  <si>
-    <t>M1</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
-  </si>
-  <si>
-    <t>Toledo melodi</t>
-  </si>
-  <si>
-    <t>2026-06-06T19:00</t>
-  </si>
-  <si>
-    <t>1154833127</t>
-  </si>
-  <si>
-    <t>Luisgabrieltoledozanhaoria@gmail.com</t>
   </si>
   <si>
     <t>cumpleaños</t>
@@ -400,7 +397,7 @@
         <v>26</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>19</v>
@@ -408,10 +405,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>28</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>29</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>2.0</v>
@@ -420,22 +417,22 @@
         <v>17</v>
       </c>
       <c r="E4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="F4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s" s="0">
+      <c r="I4" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="I4" t="s" s="0">
-        <v>32</v>
-      </c>
       <c r="J4" t="s" s="0">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="N4" t="s" s="0">
         <v>19</v>
@@ -443,10 +440,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>7.0</v>
@@ -455,22 +452,22 @@
         <v>17</v>
       </c>
       <c r="E5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J5" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="F5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s" s="0">
+      <c r="L5" t="s" s="0">
         <v>37</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="L5" t="s" s="0">
-        <v>38</v>
       </c>
       <c r="N5" t="s" s="0">
         <v>19</v>
@@ -478,121 +475,121 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="0">
         <v>39</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>40</v>
       </c>
       <c r="C6" t="n" s="0">
         <v>3.0</v>
       </c>
       <c r="D6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="E6" t="s" s="0">
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="F6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s" s="0">
+      <c r="J6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="J6" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s" s="0">
+      <c r="L6" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="L6" t="s" s="0">
+      <c r="M6" t="s" s="0">
         <v>45</v>
-      </c>
-      <c r="M6" t="s" s="0">
-        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="0">
         <v>47</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>48</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="D7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="E7" t="s" s="0">
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="F7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G7" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s" s="0">
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="J7" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="K7" t="s" s="0">
+      <c r="M7" t="s" s="0">
         <v>52</v>
-      </c>
-      <c r="M7" t="s" s="0">
-        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n" s="0">
         <v>6.0</v>
       </c>
       <c r="D8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="E8" t="s" s="0">
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="F8" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s" s="0">
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="J8" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="K8" t="s" s="0">
+      <c r="L8" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M8" t="s" s="0">
         <v>58</v>
-      </c>
-      <c r="L8" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="M8" t="s" s="0">
-        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s" s="0">
         <v>60</v>
-      </c>
-      <c r="B9" t="s" s="0">
-        <v>61</v>
       </c>
       <c r="C9" t="n" s="0">
         <v>5.0</v>
@@ -601,28 +598,28 @@
         <v>17</v>
       </c>
       <c r="E9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="F9" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G9" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H9" t="s" s="0">
+      <c r="J9" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K9" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="J9" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K9" t="s" s="0">
+      <c r="L9" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M9" t="s" s="0">
         <v>64</v>
-      </c>
-      <c r="L9" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="M9" t="s" s="0">
-        <v>65</v>
       </c>
       <c r="N9" t="s" s="0">
         <v>19</v>
@@ -630,7 +627,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s" s="0">
         <v>16</v>
@@ -642,22 +639,22 @@
         <v>17</v>
       </c>
       <c r="E10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="F10" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G10" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H10" t="s" s="0">
-        <v>68</v>
-      </c>
       <c r="J10" t="s" s="0">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="L10" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N10" t="s" s="0">
         <v>19</v>
@@ -665,10 +662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s" s="0">
         <v>69</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>70</v>
       </c>
       <c r="C11" t="n" s="0">
         <v>6.0</v>
@@ -677,7 +674,7 @@
         <v>17</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s" s="0">
         <v>19</v>
@@ -686,13 +683,13 @@
         <v>19</v>
       </c>
       <c r="H11" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J11" t="s" s="0">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="L11" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N11" t="s" s="0">
         <v>19</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,6 +59,30 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>Daniel Suppa</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Joel Quispe Criales</t>
   </si>
   <si>
@@ -71,15 +95,9 @@
     <t>1151524080</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>jhoel.n1723@gmail.com</t>
   </si>
   <si>
-    <t>CONFIRMADA</t>
-  </si>
-  <si>
     <t>Domingo 7 de Junio de 2026 a las 14:30 hs</t>
   </si>
   <si>
@@ -93,9 +111,6 @@
   </si>
   <si>
     <t>2026-06-07T13:00</t>
-  </si>
-  <si>
-    <t>Salón</t>
   </si>
   <si>
     <t>1130772468</t>
@@ -149,7 +164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -224,7 +239,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -244,49 +259,81 @@
       <c r="J2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K2" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>24</v>
+      <c r="N2" t="s" s="0">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="E3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="C3" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="D3" t="s" s="0">
+      <c r="F3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>27</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>29</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>21</v>
       </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
       <c r="M3" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="N3" t="s" s="0">
-        <v>19</v>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -68,7 +68,7 @@
     <t>Salón</t>
   </si>
   <si>
-    <t>0</t>
+    <t>1133669519</t>
   </si>
   <si>
     <t>Sí</t>
@@ -239,7 +239,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,6 +59,30 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>Juan Carlos Burga</t>
+  </si>
+  <si>
+    <t>2026-06-07T14:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+51 997672944</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>jcburga@outlook.com</t>
+  </si>
+  <si>
+    <t>Domingo 7 de Junio de 2026 a las 14:30 hs</t>
+  </si>
+  <si>
+    <t>Comida entre amigos. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
     <t>Daniel Suppa</t>
   </si>
   <si>
@@ -80,15 +104,9 @@
     <t>CONFIRMADA</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Joel Quispe Criales</t>
   </si>
   <si>
-    <t>2026-06-07T14:30:00</t>
-  </si>
-  <si>
     <t>Puerto Madero</t>
   </si>
   <si>
@@ -96,9 +114,6 @@
   </si>
   <si>
     <t>jhoel.n1723@gmail.com</t>
-  </si>
-  <si>
-    <t>Domingo 7 de Junio de 2026 a las 14:30 hs</t>
   </si>
   <si>
     <t>cumpleaños</t>
@@ -164,7 +179,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -239,7 +254,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -256,10 +271,10 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="K2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="M2" t="s" s="0">
         <v>22</v>
       </c>
     </row>
@@ -271,7 +286,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>25</v>
@@ -280,60 +295,92 @@
         <v>26</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="L3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="M3" t="s" s="0">
-        <v>30</v>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="E4" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C4" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s" s="0">
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="F4" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s" s="0">
+      <c r="J4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="J4" t="s" s="0">
-        <v>21</v>
       </c>
       <c r="M4" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="N4" t="s" s="0">
-        <v>22</v>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>ailulugones18@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
   </si>
   <si>
     <t>LUGAR LINDO</t>
@@ -374,10 +377,10 @@
         <v>39</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s" s="0">
         <v>19</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -101,21 +101,24 @@
     <t>.</t>
   </si>
   <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Joel Quispe Criales</t>
+  </si>
+  <si>
+    <t>Puerto Madero</t>
+  </si>
+  <si>
+    <t>1151524080</t>
+  </si>
+  <si>
+    <t>jhoel.n1723@gmail.com</t>
+  </si>
+  <si>
     <t>CONFIRMADA</t>
   </si>
   <si>
-    <t>Joel Quispe Criales</t>
-  </si>
-  <si>
-    <t>Puerto Madero</t>
-  </si>
-  <si>
-    <t>1151524080</t>
-  </si>
-  <si>
-    <t>jhoel.n1723@gmail.com</t>
-  </si>
-  <si>
     <t>cumpleaños</t>
   </si>
   <si>
@@ -132,9 +135,6 @@
   </si>
   <si>
     <t>ailulugones18@gmail.com</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
   </si>
   <si>
     <t>LUGAR LINDO</t>
@@ -339,24 +339,24 @@
         <v>33</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s" s="0">
         <v>21</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>6.0</v>
@@ -365,7 +365,7 @@
         <v>25</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -374,10 +374,10 @@
         <v>19</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="M5" t="s" s="0">
         <v>41</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -114,9 +114,6 @@
   </si>
   <si>
     <t>jhoel.n1723@gmail.com</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
   </si>
   <si>
     <t>cumpleaños</t>
@@ -339,24 +336,24 @@
         <v>33</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s" s="0">
         <v>21</v>
       </c>
       <c r="L4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s" s="0">
         <v>35</v>
-      </c>
-      <c r="M4" t="s" s="0">
-        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>37</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>38</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>6.0</v>
@@ -365,22 +362,22 @@
         <v>25</v>
       </c>
       <c r="E5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
         <v>39</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>40</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>29</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N5" t="s" s="0">
         <v>19</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,19 +59,40 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>Micaela Medina</t>
+  </si>
+  <si>
+    <t>2026-06-07T21:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1125931994</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>micaelamedina2412@gmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Domingo 7 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Cliente con bebé recién nacida (sin cargo, menor de 2 años).</t>
+  </si>
+  <si>
     <t>Juan Carlos Burga</t>
   </si>
   <si>
     <t>2026-06-07T14:30:00</t>
   </si>
   <si>
-    <t>Salón Principal</t>
-  </si>
-  <si>
     <t>+51 997672944</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>jcburga@outlook.com</t>
@@ -179,7 +200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -254,7 +275,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -271,43 +292,46 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
       <c r="K2" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>26</v>
       </c>
       <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="G3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s" s="0">
+      <c r="K3" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="J3" t="s" s="0">
+      <c r="M3" t="s" s="0">
         <v>29</v>
-      </c>
-      <c r="N3" t="s" s="0">
-        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -315,71 +339,103 @@
         <v>30</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="K4" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="L4" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="M4" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="C5" t="n" s="0">
+      <c r="K5" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C6" t="n" s="0">
         <v>6.0</v>
       </c>
-      <c r="D5" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="M5" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="N5" t="s" s="0">
+      <c r="D6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="N6" t="s" s="0">
         <v>19</v>
       </c>
     </row>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -98,6 +98,9 @@
     <t>jcburga@outlook.com</t>
   </si>
   <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
     <t>Domingo 7 de Junio de 2026 a las 14:30 hs</t>
   </si>
   <si>
@@ -120,9 +123,6 @@
   </si>
   <si>
     <t>.</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
   </si>
   <si>
     <t>Joel Quispe Criales</t>
@@ -327,40 +327,43 @@
       <c r="H3" t="s" s="0">
         <v>27</v>
       </c>
+      <c r="J3" t="s" s="0">
+        <v>28</v>
+      </c>
       <c r="K3" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M3" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="N4" t="s" s="0">
         <v>19</v>
@@ -392,10 +395,10 @@
         <v>40</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K5" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>41</v>
@@ -415,7 +418,7 @@
         <v>6.0</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>45</v>
@@ -430,7 +433,7 @@
         <v>46</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M6" t="s" s="0">
         <v>47</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -57,6 +57,36 @@
   </si>
   <si>
     <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Mario Schiraldi</t>
+  </si>
+  <si>
+    <t>2026-06-09T12:30:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1524593334</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>mario.schiraldi@gpc-sa.com.ar</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Martes 9 de Junio de 2026 a las 12:30 hs</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Reunión de trabajo. Sin restricciones alimentarias. Contactar al celular 1524593334.</t>
   </si>
 </sst>
 </file>
@@ -101,7 +131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -168,6 +198,44 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,6 +59,36 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>Gustavo Cesar Mollo</t>
+  </si>
+  <si>
+    <t>2026-06-09T21:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+5411 6553 5100</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>gusmollo1962@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Martes 9 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la señora del cliente. Beneficios de cumpleañera aplicables (torta simbólica, copa de champagne, no paga menú).</t>
+  </si>
+  <si>
     <t>Mario Schiraldi</t>
   </si>
   <si>
@@ -71,13 +101,7 @@
     <t>1524593334</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>mario.schiraldi@gpc-sa.com.ar</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
   </si>
   <si>
     <t>Martes 9 de Junio de 2026 a las 12:30 hs</t>
@@ -131,7 +155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -206,7 +230,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -234,6 +258,44 @@
       </c>
       <c r="M2" t="s" s="0">
         <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -92,7 +92,7 @@
     <t>Mario Schiraldi</t>
   </si>
   <si>
-    <t>2026-06-09T12:30:00</t>
+    <t>2026-06-09T13:00</t>
   </si>
   <si>
     <t>Salón</t>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>mario.schiraldi@gpc-sa.com.ar</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
   </si>
   <si>
     <t>Martes 9 de Junio de 2026 a las 12:30 hs</t>
@@ -286,16 +289,16 @@
         <v>29</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,6 +59,32 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>SERGIO GARECA</t>
+  </si>
+  <si>
+    <t>2026-06-09T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1151451430</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>sergio.gareca.c@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>21:15
+PUEDEN SER 12
+SIVERIA CERCA DE TV GRANDE</t>
+  </si>
+  <si>
     <t>Gustavo Cesar Mollo</t>
   </si>
   <si>
@@ -71,15 +97,9 @@
     <t>+5411 6553 5100</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>gusmollo1962@gmail.com</t>
   </si>
   <si>
-    <t>CONFIRMADA</t>
-  </si>
-  <si>
     <t>Martes 9 de Junio de 2026 a las 21:00 hs</t>
   </si>
   <si>
@@ -93,9 +113,6 @@
   </si>
   <si>
     <t>2026-06-09T13:00</t>
-  </si>
-  <si>
-    <t>Salón</t>
   </si>
   <si>
     <t>1524593334</t>
@@ -158,7 +175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -233,7 +250,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -253,52 +270,87 @@
       <c r="J2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="M2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="L2" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>24</v>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="E3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="C3" t="n" s="0">
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
         <v>5.0</v>
       </c>
-      <c r="D3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="J3" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="K3" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="L3" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="M3" t="s" s="0">
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
         <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -100,6 +100,9 @@
     <t>gusmollo1962@gmail.com</t>
   </si>
   <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
     <t>Martes 9 de Junio de 2026 a las 21:00 hs</t>
   </si>
   <si>
@@ -119,9 +122,6 @@
   </si>
   <si>
     <t>mario.schiraldi@gpc-sa.com.ar</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
   </si>
   <si>
     <t>Martes 9 de Junio de 2026 a las 12:30 hs</t>
@@ -303,24 +303,24 @@
         <v>27</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>5.0</v>
@@ -329,7 +329,7 @@
         <v>17</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>19</v>
@@ -338,10 +338,10 @@
         <v>19</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s" s="0">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K4" t="s" s="0">
         <v>36</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -77,7 +77,7 @@
     <t>sergio.gareca.c@gmail.com</t>
   </si>
   <si>
-    <t>CONFIRMADA</t>
+    <t>TERMINADA</t>
   </si>
   <si>
     <t>21:15
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>gusmollo1962@gmail.com</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
   </si>
   <si>
     <t>Martes 9 de Junio de 2026 a las 21:00 hs</t>
@@ -303,24 +300,24 @@
         <v>27</v>
       </c>
       <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="K3" t="s" s="0">
+      <c r="L3" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="M3" t="s" s="0">
         <v>30</v>
-      </c>
-      <c r="M3" t="s" s="0">
-        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>32</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>33</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>5.0</v>
@@ -329,28 +326,28 @@
         <v>17</v>
       </c>
       <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="F4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s" s="0">
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="J4" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="K4" t="s" s="0">
+      <c r="L4" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="L4" t="s" s="0">
+      <c r="M4" t="s" s="0">
         <v>37</v>
-      </c>
-      <c r="M4" t="s" s="0">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,75 +59,52 @@
     <t>monto_sena</t>
   </si>
   <si>
-    <t>SERGIO GARECA</t>
-  </si>
-  <si>
-    <t>2026-06-09T21:30</t>
+    <t>Tomas Della Valle</t>
+  </si>
+  <si>
+    <t>2026-06-10T22:00:00</t>
+  </si>
+  <si>
+    <t>A definir por el local</t>
+  </si>
+  <si>
+    <t>2213188160</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>todellavalle@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Miércoles 10 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita romántica con pareja. Promo Miércoles $50.000 + servicio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estanislao </t>
+  </si>
+  <si>
+    <t>2026-06-10T20:30</t>
   </si>
   <si>
     <t>Salón</t>
   </si>
   <si>
-    <t>1151451430</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>sergio.gareca.c@gmail.com</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
-  </si>
-  <si>
-    <t>21:15
-PUEDEN SER 12
-SIVERIA CERCA DE TV GRANDE</t>
-  </si>
-  <si>
-    <t>Gustavo Cesar Mollo</t>
-  </si>
-  <si>
-    <t>2026-06-09T21:00:00</t>
-  </si>
-  <si>
-    <t>Salón Principal</t>
-  </si>
-  <si>
-    <t>+5411 6553 5100</t>
-  </si>
-  <si>
-    <t>gusmollo1962@gmail.com</t>
-  </si>
-  <si>
-    <t>Martes 9 de Junio de 2026 a las 21:00 hs</t>
-  </si>
-  <si>
-    <t>cumpleaños</t>
-  </si>
-  <si>
-    <t>Cumpleaños de la señora del cliente. Beneficios de cumpleañera aplicables (torta simbólica, copa de champagne, no paga menú).</t>
-  </si>
-  <si>
-    <t>Mario Schiraldi</t>
-  </si>
-  <si>
-    <t>2026-06-09T13:00</t>
-  </si>
-  <si>
-    <t>1524593334</t>
-  </si>
-  <si>
-    <t>mario.schiraldi@gpc-sa.com.ar</t>
-  </si>
-  <si>
-    <t>Martes 9 de Junio de 2026 a las 12:30 hs</t>
-  </si>
-  <si>
-    <t>negocios</t>
-  </si>
-  <si>
-    <t>Reunión de trabajo. Sin restricciones alimentarias. Contactar al celular 1524593334.</t>
+    <t>5492975163812</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
   </si>
 </sst>
 </file>
@@ -172,7 +149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -247,7 +224,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -267,28 +244,31 @@
       <c r="J2" t="s" s="0">
         <v>21</v>
       </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
       <c r="M2" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="N2" t="s" s="0">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>19</v>
@@ -297,57 +277,16 @@
         <v>19</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K3" t="s" s="0">
-        <v>28</v>
-      </c>
       <c r="L3" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s" s="0">
         <v>30</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="J4" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="L4" t="s" s="0">
-        <v>36</v>
-      </c>
-      <c r="M4" t="s" s="0">
-        <v>37</v>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,6 +59,33 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>stella Gualinchay</t>
+  </si>
+  <si>
+    <t>2026-06-10T21:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1138669334</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>un cumpleañero, quizas consigan dos personas mas para la promocion</t>
+  </si>
+  <si>
     <t>Tomas Della Valle</t>
   </si>
   <si>
@@ -71,15 +98,9 @@
     <t>2213188160</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>todellavalle@gmail.com</t>
   </si>
   <si>
-    <t>CONFIRMADA</t>
-  </si>
-  <si>
     <t>Miércoles 10 de Junio de 2026 a las 22:00 hs</t>
   </si>
   <si>
@@ -93,9 +114,6 @@
   </si>
   <si>
     <t>2026-06-10T20:30</t>
-  </si>
-  <si>
-    <t>Salón</t>
   </si>
   <si>
     <t>5492975163812</t>
@@ -149,7 +167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -224,7 +242,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -241,51 +259,89 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
       <c r="J2" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="M2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="M2" t="s" s="0">
-        <v>24</v>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="C3" t="n" s="0">
-        <v>10.0</v>
-      </c>
-      <c r="D3" t="s" s="0">
+      <c r="E3" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s" s="0">
         <v>29</v>
-      </c>
-      <c r="J3" t="s" s="0">
-        <v>21</v>
       </c>
       <c r="L3" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="N3" t="s" s="0">
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s" s="0">
         <v>19</v>
       </c>
     </row>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,28 +59,40 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>Daiana Leal</t>
+  </si>
+  <si>
+    <t>2026-06-10T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>118203547</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
     <t>stella Gualinchay</t>
   </si>
   <si>
     <t>2026-06-10T21:00</t>
   </si>
   <si>
-    <t>Salón</t>
-  </si>
-  <si>
     <t>1138669334</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
     <t>M9</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
   </si>
   <si>
     <t>un cumpleañero, quizas consigan dos personas mas para la promocion</t>
@@ -167,7 +179,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -242,7 +254,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -265,83 +277,118 @@
       <c r="J2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="M2" t="s" s="0">
-        <v>23</v>
-      </c>
       <c r="N2" t="s" s="0">
         <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="C3" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="D3" t="s" s="0">
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s" s="0">
         <v>26</v>
-      </c>
-      <c r="E3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>28</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="K3" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s" s="0">
-        <v>30</v>
-      </c>
       <c r="M3" t="s" s="0">
-        <v>31</v>
+        <v>27</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
         <v>32</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>10.0</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>35</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>22</v>
       </c>
+      <c r="K4" t="s" s="0">
+        <v>33</v>
+      </c>
       <c r="L4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="N4" t="s" s="0">
+      <c r="B5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="N5" t="s" s="0">
         <v>19</v>
       </c>
     </row>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>M9</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
   </si>
   <si>
     <t>un cumpleañero, quizas consigan dos personas mas para la promocion</t>
@@ -289,7 +292,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>17</v>
@@ -310,10 +313,10 @@
         <v>26</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>19</v>
@@ -321,19 +324,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>19</v>
@@ -342,27 +345,27 @@
         <v>19</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>22</v>
       </c>
       <c r="K4" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M4" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C5" t="n" s="0">
         <v>10.0</v>
@@ -371,7 +374,7 @@
         <v>17</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -380,13 +383,13 @@
         <v>19</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>22</v>
       </c>
       <c r="L5" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s" s="0">
         <v>19</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -80,40 +80,40 @@
     <t>M1</t>
   </si>
   <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>stella Gualinchay</t>
+  </si>
+  <si>
+    <t>2026-06-10T21:00</t>
+  </si>
+  <si>
+    <t>1138669334</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>un cumpleañero, quizas consigan dos personas mas para la promocion</t>
+  </si>
+  <si>
+    <t>Tomas Della Valle</t>
+  </si>
+  <si>
+    <t>2026-06-10T22:00:00</t>
+  </si>
+  <si>
+    <t>A definir por el local</t>
+  </si>
+  <si>
+    <t>2213188160</t>
+  </si>
+  <si>
+    <t>todellavalle@gmail.com</t>
+  </si>
+  <si>
     <t>CONFIRMADA</t>
-  </si>
-  <si>
-    <t>stella Gualinchay</t>
-  </si>
-  <si>
-    <t>2026-06-10T21:00</t>
-  </si>
-  <si>
-    <t>1138669334</t>
-  </si>
-  <si>
-    <t>M9</t>
-  </si>
-  <si>
-    <t>CANCELADA</t>
-  </si>
-  <si>
-    <t>un cumpleañero, quizas consigan dos personas mas para la promocion</t>
-  </si>
-  <si>
-    <t>Tomas Della Valle</t>
-  </si>
-  <si>
-    <t>2026-06-10T22:00:00</t>
-  </si>
-  <si>
-    <t>A definir por el local</t>
-  </si>
-  <si>
-    <t>2213188160</t>
-  </si>
-  <si>
-    <t>todellavalle@gmail.com</t>
   </si>
   <si>
     <t>Miércoles 10 de Junio de 2026 a las 22:00 hs</t>
@@ -313,10 +313,10 @@
         <v>26</v>
       </c>
       <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s" s="0">
         <v>27</v>
-      </c>
-      <c r="M3" t="s" s="0">
-        <v>28</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>19</v>
@@ -324,31 +324,31 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="0">
         <v>29</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>30</v>
       </c>
       <c r="C4" t="n" s="0">
         <v>2.0</v>
       </c>
       <c r="D4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="E4" t="s" s="0">
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="F4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s" s="0">
+      <c r="J4" t="s" s="0">
         <v>33</v>
-      </c>
-      <c r="J4" t="s" s="0">
-        <v>22</v>
       </c>
       <c r="K4" t="s" s="0">
         <v>34</v>
@@ -386,7 +386,7 @@
         <v>40</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L5" t="s" s="0">
         <v>41</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,85 +59,49 @@
     <t>monto_sena</t>
   </si>
   <si>
-    <t>Daiana Leal</t>
-  </si>
-  <si>
-    <t>2026-06-10T21:30</t>
+    <t xml:space="preserve">NOVORIENTE </t>
+  </si>
+  <si>
+    <t>2026-06-11T12:30</t>
   </si>
   <si>
     <t>Salón</t>
   </si>
   <si>
-    <t>118203547</t>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9+1 GUIA $48000 INCLUYE 1 AGUA O GASEOSA </t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>M1</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
-  </si>
-  <si>
-    <t>stella Gualinchay</t>
-  </si>
-  <si>
-    <t>2026-06-10T21:00</t>
-  </si>
-  <si>
-    <t>1138669334</t>
-  </si>
-  <si>
-    <t>M9</t>
-  </si>
-  <si>
-    <t>un cumpleañero, quizas consigan dos personas mas para la promocion</t>
-  </si>
-  <si>
-    <t>Tomas Della Valle</t>
-  </si>
-  <si>
-    <t>2026-06-10T22:00:00</t>
-  </si>
-  <si>
-    <t>A definir por el local</t>
-  </si>
-  <si>
-    <t>2213188160</t>
-  </si>
-  <si>
-    <t>todellavalle@gmail.com</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
-  </si>
-  <si>
-    <t>Miércoles 10 de Junio de 2026 a las 22:00 hs</t>
-  </si>
-  <si>
-    <t>cita</t>
-  </si>
-  <si>
-    <t>Cita romántica con pareja. Promo Miércoles $50.000 + servicio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estanislao </t>
-  </si>
-  <si>
-    <t>2026-06-10T20:30</t>
-  </si>
-  <si>
-    <t>5492975163812</t>
+    <t xml:space="preserve">Paranature </t>
+  </si>
+  <si>
+    <t>2026-06-11T21:00</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>otra</t>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>cub x $54.000 (agua o gaseosa 1) - transf (3 lib)</t>
   </si>
 </sst>
 </file>
@@ -182,7 +146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -257,7 +221,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -274,125 +238,58 @@
       <c r="H2" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="J2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="L2" t="s" s="0">
         <v>22</v>
       </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
       <c r="N2" t="s" s="0">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>17</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>28</v>
       </c>
       <c r="M3" t="s" s="0">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>19</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="C4" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="J4" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="K4" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="L4" t="s" s="0">
-        <v>35</v>
-      </c>
-      <c r="M4" t="s" s="0">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="C5" t="n" s="0">
-        <v>10.0</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>39</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s" s="0">
-        <v>40</v>
-      </c>
-      <c r="J5" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="L5" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="N5" t="s" s="0">
-        <v>19</v>
+      <c r="O3" t="n" s="0">
+        <v>800000.0</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -86,16 +86,16 @@
     <t xml:space="preserve">9+1 GUIA $48000 INCLUYE 1 AGUA O GASEOSA </t>
   </si>
   <si>
+    <t xml:space="preserve">Paranature </t>
+  </si>
+  <si>
+    <t>2026-06-11T21:00</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paranature </t>
-  </si>
-  <si>
-    <t>2026-06-11T21:00</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>celebracion_grupo</t>
@@ -248,15 +248,18 @@
         <v>23</v>
       </c>
       <c r="N2" t="s" s="0">
-        <v>24</v>
+        <v>19</v>
+      </c>
+      <c r="O2" t="n" s="0">
+        <v>432000.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>25</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>26</v>
       </c>
       <c r="C3" t="n" s="0">
         <v>25.0</v>
@@ -265,16 +268,16 @@
         <v>17</v>
       </c>
       <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="F3" t="s" s="0">
-        <v>24</v>
-      </c>
       <c r="G3" t="s" s="0">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>21</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -77,25 +77,28 @@
     <t>.</t>
   </si>
   <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9+1 GUIA $48000 INCLUYE 1 AGUA O GASEOSA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paranature </t>
+  </si>
+  <si>
+    <t>2026-06-11T21:00</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>CONFIRMADA</t>
-  </si>
-  <si>
-    <t>otra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9+1 GUIA $48000 INCLUYE 1 AGUA O GASEOSA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paranature </t>
-  </si>
-  <si>
-    <t>2026-06-11T21:00</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>celebracion_grupo</t>
@@ -280,13 +283,13 @@
         <v>26</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L3" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M3" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>19</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>No</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
   </si>
   <si>
     <t>celebracion_grupo</t>
@@ -283,13 +280,13 @@
         <v>26</v>
       </c>
       <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="M3" t="s" s="0">
         <v>29</v>
-      </c>
-      <c r="M3" t="s" s="0">
-        <v>30</v>
       </c>
       <c r="N3" t="s" s="0">
         <v>19</v>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,49 +59,73 @@
     <t>monto_sena</t>
   </si>
   <si>
-    <t xml:space="preserve">NOVORIENTE </t>
-  </si>
-  <si>
-    <t>2026-06-11T12:30</t>
+    <t>FIORELLA AVILA</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30</t>
   </si>
   <si>
     <t>Salón</t>
   </si>
   <si>
-    <t>1153364142</t>
+    <t>1131906911</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>avilafiorella98@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>CUMPLEAÑOS</t>
+  </si>
+  <si>
+    <t>Marcelo Escobar</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>+595992433328</t>
+  </si>
+  <si>
+    <t>chelolopezescobar@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente quiere ver partido en Dique. Aniversario.</t>
+  </si>
+  <si>
+    <t>Antonela Bravo</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00</t>
+  </si>
+  <si>
+    <t>1139502659</t>
+  </si>
+  <si>
+    <t>tdganto@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>20 aprox.</t>
   </si>
   <si>
     <t>Sí</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
-  </si>
-  <si>
-    <t>otra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9+1 GUIA $48000 INCLUYE 1 AGUA O GASEOSA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paranature </t>
-  </si>
-  <si>
-    <t>2026-06-11T21:00</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>celebracion_grupo</t>
-  </si>
-  <si>
-    <t>cub x $54.000 (agua o gaseosa 1) - transf (3 lib)</t>
   </si>
 </sst>
 </file>
@@ -146,7 +170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -221,7 +245,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -241,58 +265,90 @@
       <c r="J2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="M2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="M2" t="s" s="0">
-        <v>23</v>
-      </c>
       <c r="N2" t="s" s="0">
         <v>19</v>
-      </c>
-      <c r="O2" t="n" s="0">
-        <v>432000.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>25</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>25.0</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>17</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>26</v>
       </c>
       <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>27</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>26</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>21</v>
       </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
       <c r="L3" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M3" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="N3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="O3" t="n" s="0">
-        <v>800000.0</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>100000.0</v>
       </c>
     </row>
   </sheetData>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,6 +59,30 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>Lucila Salem</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1132464079</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>salem.lucila@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
     <t>FIORELLA AVILA</t>
   </si>
   <si>
@@ -71,13 +95,7 @@
     <t>1131906911</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>avilafiorella98@gmail.com</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
   </si>
   <si>
     <t>CUMPLEAÑOS</t>
@@ -170,7 +188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -245,7 +263,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -265,11 +283,8 @@
       <c r="J2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="K2" t="s" s="0">
         <v>22</v>
-      </c>
-      <c r="N2" t="s" s="0">
-        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -280,7 +295,7 @@
         <v>24</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>25</v>
@@ -300,54 +315,89 @@
       <c r="J3" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K3" t="s" s="0">
+      <c r="M3" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="L3" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s" s="0">
-        <v>30</v>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="E4" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="C4" t="n" s="0">
-        <v>20.0</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s" s="0">
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
         <v>33</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>34</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>21</v>
       </c>
+      <c r="K4" t="s" s="0">
+        <v>34</v>
+      </c>
       <c r="L4" t="s" s="0">
         <v>35</v>
       </c>
       <c r="M4" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="N4" t="s" s="0">
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="O4" t="n" s="0">
+      <c r="B5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="O5" t="n" s="0">
         <v>100000.0</v>
       </c>
     </row>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,6 +59,36 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>Cid Nayo Borges Santos</t>
+  </si>
+  <si>
+    <t>2026-06-12T20:30:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1131940422</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Geovanapimemta2004@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial. Cliente prefirió sector Siberia para ambiente íntimo.</t>
+  </si>
+  <si>
     <t>Lucila Salem</t>
   </si>
   <si>
@@ -71,13 +101,7 @@
     <t>1132464079</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>salem.lucila@gmail.com</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
   </si>
   <si>
     <t>Viernes 12 de Junio de 2026 a las 21:30 hs</t>
@@ -188,7 +212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -263,7 +287,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>17</v>
@@ -286,22 +310,28 @@
       <c r="K2" t="s" s="0">
         <v>22</v>
       </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s" s="0">
         <v>19</v>
@@ -310,33 +340,30 @@
         <v>19</v>
       </c>
       <c r="H3" t="s" s="0">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="M3" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="N3" t="s" s="0">
-        <v>19</v>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>19</v>
@@ -345,19 +372,16 @@
         <v>19</v>
       </c>
       <c r="H4" t="s" s="0">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K4" t="s" s="0">
-        <v>34</v>
-      </c>
-      <c r="L4" t="s" s="0">
-        <v>35</v>
-      </c>
       <c r="M4" t="s" s="0">
         <v>36</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -368,13 +392,13 @@
         <v>38</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s" s="0">
         <v>19</v>
@@ -383,21 +407,59 @@
         <v>19</v>
       </c>
       <c r="H5" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s" s="0">
         <v>21</v>
       </c>
+      <c r="K5" t="s" s="0">
+        <v>42</v>
+      </c>
       <c r="L5" t="s" s="0">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s" s="0">
-        <v>42</v>
-      </c>
-      <c r="N5" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="O5" t="n" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="O6" t="n" s="0">
         <v>100000.0</v>
       </c>
     </row>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="58">
   <si>
     <t>nombre y apellido</t>
   </si>
@@ -59,6 +59,33 @@
     <t>monto_sena</t>
   </si>
   <si>
+    <t>Tomás Castro</t>
+  </si>
+  <si>
+    <t>2026-06-12T22:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+54 9 297 4 17 16 70</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tommycass55@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>Cena con hermano. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
     <t>Cid Nayo Borges Santos</t>
   </si>
   <si>
@@ -71,15 +98,9 @@
     <t>1131940422</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Geovanapimemta2004@gmail.com</t>
   </si>
   <si>
-    <t>CONFIRMADA</t>
-  </si>
-  <si>
     <t>Viernes 12 de Junio de 2026 a las 20:30 hs</t>
   </si>
   <si>
@@ -93,9 +114,6 @@
   </si>
   <si>
     <t>2026-06-12T21:30:00</t>
-  </si>
-  <si>
-    <t>Salón Principal</t>
   </si>
   <si>
     <t>1132464079</t>
@@ -212,7 +230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -310,57 +328,60 @@
       <c r="K2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="M2" t="s" s="0">
         <v>23</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="C3" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="D3" t="s" s="0">
+      <c r="E3" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="E3" t="s" s="0">
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
         <v>28</v>
-      </c>
-      <c r="F3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>29</v>
       </c>
       <c r="J3" t="s" s="0">
         <v>21</v>
       </c>
       <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
         <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>34</v>
@@ -377,11 +398,8 @@
       <c r="J4" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="M4" t="s" s="0">
+      <c r="K4" t="s" s="0">
         <v>36</v>
-      </c>
-      <c r="N4" t="s" s="0">
-        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -392,7 +410,7 @@
         <v>38</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>39</v>
@@ -412,54 +430,89 @@
       <c r="J5" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="K5" t="s" s="0">
+      <c r="M5" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="L5" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="M5" t="s" s="0">
-        <v>44</v>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="E6" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="C6" t="n" s="0">
-        <v>20.0</v>
-      </c>
-      <c r="D6" t="s" s="0">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s" s="0">
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
         <v>47</v>
-      </c>
-      <c r="F6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G6" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s" s="0">
-        <v>48</v>
       </c>
       <c r="J6" t="s" s="0">
         <v>21</v>
       </c>
+      <c r="K6" t="s" s="0">
+        <v>48</v>
+      </c>
       <c r="L6" t="s" s="0">
         <v>49</v>
       </c>
       <c r="M6" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="N6" t="s" s="0">
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="O6" t="n" s="0">
+      <c r="B7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="O7" t="n" s="0">
         <v>100000.0</v>
       </c>
     </row>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="58">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,145 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Tomás Castro</t>
+  </si>
+  <si>
+    <t>2026-06-12T22:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+54 9 297 4 17 16 70</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tommycass55@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>Cena con hermano. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Cid Nayo Borges Santos</t>
+  </si>
+  <si>
+    <t>2026-06-12T20:30:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1131940422</t>
+  </si>
+  <si>
+    <t>Geovanapimemta2004@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial. Cliente prefirió sector Siberia para ambiente íntimo.</t>
+  </si>
+  <si>
+    <t>Lucila Salem</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30:00</t>
+  </si>
+  <si>
+    <t>1132464079</t>
+  </si>
+  <si>
+    <t>salem.lucila@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>FIORELLA AVILA</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1131906911</t>
+  </si>
+  <si>
+    <t>avilafiorella98@gmail.com</t>
+  </si>
+  <si>
+    <t>CUMPLEAÑOS</t>
+  </si>
+  <si>
+    <t>Marcelo Escobar</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>+595992433328</t>
+  </si>
+  <si>
+    <t>chelolopezescobar@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente quiere ver partido en Dique. Aniversario.</t>
+  </si>
+  <si>
+    <t>Antonela Bravo</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00</t>
+  </si>
+  <si>
+    <t>1139502659</t>
+  </si>
+  <si>
+    <t>tdganto@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>20 aprox.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +245,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +287,234 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>100000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,148 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Tomás Castro</t>
+  </si>
+  <si>
+    <t>2026-06-12T22:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+54 9 297 4 17 16 70</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tommycass55@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>Cena con hermano. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Cid Nayo Borges Santos</t>
+  </si>
+  <si>
+    <t>2026-06-12T20:30:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1131940422</t>
+  </si>
+  <si>
+    <t>Geovanapimemta2004@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial. Cliente prefirió sector Siberia para ambiente íntimo.</t>
+  </si>
+  <si>
+    <t>Lucila Salem</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30:00</t>
+  </si>
+  <si>
+    <t>1132464079</t>
+  </si>
+  <si>
+    <t>salem.lucila@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>FIORELLA AVILA</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1131906911</t>
+  </si>
+  <si>
+    <t>avilafiorella98@gmail.com</t>
+  </si>
+  <si>
+    <t>CUMPLEAÑOS</t>
+  </si>
+  <si>
+    <t>Marcelo Escobar</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>+595992433328</t>
+  </si>
+  <si>
+    <t>chelolopezescobar@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente quiere ver partido en Dique. Aniversario.</t>
+  </si>
+  <si>
+    <t>Antonela Bravo</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00</t>
+  </si>
+  <si>
+    <t>1139502659</t>
+  </si>
+  <si>
+    <t>tdganto@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>20 aprox.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +248,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +290,234 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>100000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,148 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Tomás Castro</t>
+  </si>
+  <si>
+    <t>2026-06-12T22:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+54 9 297 4 17 16 70</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tommycass55@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>Cena con hermano. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Cid Nayo Borges Santos</t>
+  </si>
+  <si>
+    <t>2026-06-12T20:30:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1131940422</t>
+  </si>
+  <si>
+    <t>Geovanapimemta2004@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial. Cliente prefirió sector Siberia para ambiente íntimo.</t>
+  </si>
+  <si>
+    <t>Lucila Salem</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30:00</t>
+  </si>
+  <si>
+    <t>1132464079</t>
+  </si>
+  <si>
+    <t>salem.lucila@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>FIORELLA AVILA</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1131906911</t>
+  </si>
+  <si>
+    <t>avilafiorella98@gmail.com</t>
+  </si>
+  <si>
+    <t>CUMPLEAÑOS</t>
+  </si>
+  <si>
+    <t>Marcelo Escobar</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>+595992433328</t>
+  </si>
+  <si>
+    <t>chelolopezescobar@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente quiere ver partido en Dique. Aniversario.</t>
+  </si>
+  <si>
+    <t>Antonela Bravo</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00</t>
+  </si>
+  <si>
+    <t>1139502659</t>
+  </si>
+  <si>
+    <t>tdganto@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>20 aprox.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +248,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +290,234 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>100000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,148 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Tomás Castro</t>
+  </si>
+  <si>
+    <t>2026-06-12T22:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+54 9 297 4 17 16 70</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tommycass55@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>Cena con hermano. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Cid Nayo Borges Santos</t>
+  </si>
+  <si>
+    <t>2026-06-12T20:30:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1131940422</t>
+  </si>
+  <si>
+    <t>Geovanapimemta2004@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial. Cliente prefirió sector Siberia para ambiente íntimo.</t>
+  </si>
+  <si>
+    <t>Lucila Salem</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30:00</t>
+  </si>
+  <si>
+    <t>1132464079</t>
+  </si>
+  <si>
+    <t>salem.lucila@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>FIORELLA AVILA</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1131906911</t>
+  </si>
+  <si>
+    <t>avilafiorella98@gmail.com</t>
+  </si>
+  <si>
+    <t>CUMPLEAÑOS</t>
+  </si>
+  <si>
+    <t>Marcelo Escobar</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>+595992433328</t>
+  </si>
+  <si>
+    <t>chelolopezescobar@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente quiere ver partido en Dique. Aniversario.</t>
+  </si>
+  <si>
+    <t>Antonela Bravo</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00</t>
+  </si>
+  <si>
+    <t>1139502659</t>
+  </si>
+  <si>
+    <t>tdganto@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>20 aprox.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +248,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +290,234 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>100000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,148 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Tomás Castro</t>
+  </si>
+  <si>
+    <t>2026-06-12T22:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+54 9 297 4 17 16 70</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tommycass55@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>Cena con hermano. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Cid Nayo Borges Santos</t>
+  </si>
+  <si>
+    <t>2026-06-12T20:30:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1131940422</t>
+  </si>
+  <si>
+    <t>Geovanapimemta2004@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial. Cliente prefirió sector Siberia para ambiente íntimo.</t>
+  </si>
+  <si>
+    <t>Lucila Salem</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30:00</t>
+  </si>
+  <si>
+    <t>1132464079</t>
+  </si>
+  <si>
+    <t>salem.lucila@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>FIORELLA AVILA</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1131906911</t>
+  </si>
+  <si>
+    <t>avilafiorella98@gmail.com</t>
+  </si>
+  <si>
+    <t>CUMPLEAÑOS</t>
+  </si>
+  <si>
+    <t>Marcelo Escobar</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>+595992433328</t>
+  </si>
+  <si>
+    <t>chelolopezescobar@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 12 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente quiere ver partido en Dique. Aniversario.</t>
+  </si>
+  <si>
+    <t>Antonela Bravo</t>
+  </si>
+  <si>
+    <t>2026-06-12T21:00</t>
+  </si>
+  <si>
+    <t>1139502659</t>
+  </si>
+  <si>
+    <t>tdganto@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>20 aprox.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +248,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +290,234 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>100000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,121 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alejandro araujo</t>
+  </si>
+  <si>
+    <t>2026-06-13T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1127107738</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Fernando Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T12:30:00</t>
+  </si>
+  <si>
+    <t>Sin asignación - Sábado</t>
+  </si>
+  <si>
+    <t>1164037680</t>
+  </si>
+  <si>
+    <t>Fernando_angel_88@hotmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 12:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Reunión de amigos. Cliente prefiere vista al dique — confirmar disponibilidad en local (sábado, sin asignación sectorial).</t>
+  </si>
+  <si>
+    <t>María del mar rico</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30</t>
+  </si>
+  <si>
+    <t>1170599048</t>
+  </si>
+  <si>
+    <t>steven.ledesma01@uceva.edu.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>traen torta de cumpleaños</t>
+  </si>
+  <si>
+    <t>Nahir Figueroa</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1150357273</t>
+  </si>
+  <si>
+    <t>nahir.figueroa98@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lorena. Lorena no paga cubierto (5+ adultos confirmados). Recibe torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emilia Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:00</t>
+  </si>
+  <si>
+    <t>+54 9 11 5151-7737</t>
+  </si>
+  <si>
+    <t>emiliaadiaz@gmail.com</t>
+  </si>
+  <si>
+    <t>10 a 12 personas.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +221,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +263,202 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>150000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,136 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexander Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1556456253</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Al_re88@hotmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial</t>
+  </si>
+  <si>
+    <t>Alejandro araujo</t>
+  </si>
+  <si>
+    <t>2026-06-13T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1127107738</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>Fernando Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T12:30:00</t>
+  </si>
+  <si>
+    <t>Sin asignación - Sábado</t>
+  </si>
+  <si>
+    <t>1164037680</t>
+  </si>
+  <si>
+    <t>Fernando_angel_88@hotmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 12:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Reunión de amigos. Cliente prefiere vista al dique — confirmar disponibilidad en local (sábado, sin asignación sectorial).</t>
+  </si>
+  <si>
+    <t>María del mar rico</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30</t>
+  </si>
+  <si>
+    <t>1170599048</t>
+  </si>
+  <si>
+    <t>steven.ledesma01@uceva.edu.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>traen torta de cumpleaños</t>
+  </si>
+  <si>
+    <t>Nahir Figueroa</t>
+  </si>
+  <si>
+    <t>1150357273</t>
+  </si>
+  <si>
+    <t>nahir.figueroa98@gmail.com</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lorena. Lorena no paga cubierto (5+ adultos confirmados). Recibe torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emilia Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:00</t>
+  </si>
+  <si>
+    <t>+54 9 11 5151-7737</t>
+  </si>
+  <si>
+    <t>emiliaadiaz@gmail.com</t>
+  </si>
+  <si>
+    <t>10 a 12 personas.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +236,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +278,240 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>150000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,139 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexander Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1556456253</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Al_re88@hotmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial</t>
+  </si>
+  <si>
+    <t>Alejandro araujo</t>
+  </si>
+  <si>
+    <t>2026-06-13T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1127107738</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>Fernando Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T12:30:00</t>
+  </si>
+  <si>
+    <t>Sin asignación - Sábado</t>
+  </si>
+  <si>
+    <t>1164037680</t>
+  </si>
+  <si>
+    <t>Fernando_angel_88@hotmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 12:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Reunión de amigos. Cliente prefiere vista al dique — confirmar disponibilidad en local (sábado, sin asignación sectorial).</t>
+  </si>
+  <si>
+    <t>María del mar rico</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30</t>
+  </si>
+  <si>
+    <t>1170599048</t>
+  </si>
+  <si>
+    <t>steven.ledesma01@uceva.edu.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>traen torta de cumpleaños</t>
+  </si>
+  <si>
+    <t>Nahir Figueroa</t>
+  </si>
+  <si>
+    <t>1150357273</t>
+  </si>
+  <si>
+    <t>nahir.figueroa98@gmail.com</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lorena. Lorena no paga cubierto (5+ adultos confirmados). Recibe torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emilia Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:00</t>
+  </si>
+  <si>
+    <t>+54 9 11 5151-7737</t>
+  </si>
+  <si>
+    <t>emiliaadiaz@gmail.com</t>
+  </si>
+  <si>
+    <t>10 a 12 personas.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +239,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +281,240 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>150000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,139 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexander Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1556456253</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Al_re88@hotmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial</t>
+  </si>
+  <si>
+    <t>Alejandro araujo</t>
+  </si>
+  <si>
+    <t>2026-06-13T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1127107738</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>Fernando Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T12:30:00</t>
+  </si>
+  <si>
+    <t>Sin asignación - Sábado</t>
+  </si>
+  <si>
+    <t>1164037680</t>
+  </si>
+  <si>
+    <t>Fernando_angel_88@hotmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 12:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Reunión de amigos. Cliente prefiere vista al dique — confirmar disponibilidad en local (sábado, sin asignación sectorial).</t>
+  </si>
+  <si>
+    <t>María del mar rico</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30</t>
+  </si>
+  <si>
+    <t>1170599048</t>
+  </si>
+  <si>
+    <t>steven.ledesma01@uceva.edu.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>traen torta de cumpleaños</t>
+  </si>
+  <si>
+    <t>Nahir Figueroa</t>
+  </si>
+  <si>
+    <t>1150357273</t>
+  </si>
+  <si>
+    <t>nahir.figueroa98@gmail.com</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lorena. Lorena no paga cubierto (5+ adultos confirmados). Recibe torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emilia Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:00</t>
+  </si>
+  <si>
+    <t>+54 9 11 5151-7737</t>
+  </si>
+  <si>
+    <t>emiliaadiaz@gmail.com</t>
+  </si>
+  <si>
+    <t>10 a 12 personas.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +239,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +281,240 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>150000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,139 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexander Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1556456253</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Al_re88@hotmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial</t>
+  </si>
+  <si>
+    <t>Alejandro araujo</t>
+  </si>
+  <si>
+    <t>2026-06-13T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1127107738</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>Fernando Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T12:30:00</t>
+  </si>
+  <si>
+    <t>Sin asignación - Sábado</t>
+  </si>
+  <si>
+    <t>1164037680</t>
+  </si>
+  <si>
+    <t>Fernando_angel_88@hotmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 12:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Reunión de amigos. Cliente prefiere vista al dique — confirmar disponibilidad en local (sábado, sin asignación sectorial).</t>
+  </si>
+  <si>
+    <t>María del mar rico</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30</t>
+  </si>
+  <si>
+    <t>1170599048</t>
+  </si>
+  <si>
+    <t>steven.ledesma01@uceva.edu.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>traen torta de cumpleaños</t>
+  </si>
+  <si>
+    <t>Nahir Figueroa</t>
+  </si>
+  <si>
+    <t>1150357273</t>
+  </si>
+  <si>
+    <t>nahir.figueroa98@gmail.com</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lorena. Lorena no paga cubierto (5+ adultos confirmados). Recibe torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emilia Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:00</t>
+  </si>
+  <si>
+    <t>+54 9 11 5151-7737</t>
+  </si>
+  <si>
+    <t>emiliaadiaz@gmail.com</t>
+  </si>
+  <si>
+    <t>10 a 12 personas.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +239,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +281,240 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>150000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,139 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexander Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1556456253</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Al_re88@hotmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial</t>
+  </si>
+  <si>
+    <t>Alejandro araujo</t>
+  </si>
+  <si>
+    <t>2026-06-13T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1127107738</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Fernando Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T12:30:00</t>
+  </si>
+  <si>
+    <t>Sin asignación - Sábado</t>
+  </si>
+  <si>
+    <t>1164037680</t>
+  </si>
+  <si>
+    <t>Fernando_angel_88@hotmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 12:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Reunión de amigos. Cliente prefiere vista al dique — confirmar disponibilidad en local (sábado, sin asignación sectorial).</t>
+  </si>
+  <si>
+    <t>María del mar rico</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30</t>
+  </si>
+  <si>
+    <t>1170599048</t>
+  </si>
+  <si>
+    <t>steven.ledesma01@uceva.edu.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>traen torta de cumpleaños</t>
+  </si>
+  <si>
+    <t>Nahir Figueroa</t>
+  </si>
+  <si>
+    <t>1150357273</t>
+  </si>
+  <si>
+    <t>nahir.figueroa98@gmail.com</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lorena. Lorena no paga cubierto (5+ adultos confirmados). Recibe torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emilia Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:00</t>
+  </si>
+  <si>
+    <t>+54 9 11 5151-7737</t>
+  </si>
+  <si>
+    <t>emiliaadiaz@gmail.com</t>
+  </si>
+  <si>
+    <t>10 a 12 personas.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +239,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +281,240 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>150000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,139 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexander Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1556456253</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Al_re88@hotmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial</t>
+  </si>
+  <si>
+    <t>Alejandro araujo</t>
+  </si>
+  <si>
+    <t>2026-06-13T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1127107738</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Fernando Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T12:30:00</t>
+  </si>
+  <si>
+    <t>Sin asignación - Sábado</t>
+  </si>
+  <si>
+    <t>1164037680</t>
+  </si>
+  <si>
+    <t>Fernando_angel_88@hotmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 12:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Reunión de amigos. Cliente prefiere vista al dique — confirmar disponibilidad en local (sábado, sin asignación sectorial).</t>
+  </si>
+  <si>
+    <t>María del mar rico</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30</t>
+  </si>
+  <si>
+    <t>1170599048</t>
+  </si>
+  <si>
+    <t>steven.ledesma01@uceva.edu.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>traen torta de cumpleaños</t>
+  </si>
+  <si>
+    <t>Nahir Figueroa</t>
+  </si>
+  <si>
+    <t>1150357273</t>
+  </si>
+  <si>
+    <t>nahir.figueroa98@gmail.com</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lorena. Lorena no paga cubierto (5+ adultos confirmados). Recibe torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emilia Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:00</t>
+  </si>
+  <si>
+    <t>+54 9 11 5151-7737</t>
+  </si>
+  <si>
+    <t>emiliaadiaz@gmail.com</t>
+  </si>
+  <si>
+    <t>10 a 12 personas.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +239,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +281,240 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>150000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="56">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,139 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexander Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1556456253</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Al_re88@hotmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial</t>
+  </si>
+  <si>
+    <t>Alejandro araujo</t>
+  </si>
+  <si>
+    <t>2026-06-13T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1127107738</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Fernando Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T12:30:00</t>
+  </si>
+  <si>
+    <t>Sin asignación - Sábado</t>
+  </si>
+  <si>
+    <t>1164037680</t>
+  </si>
+  <si>
+    <t>Fernando_angel_88@hotmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 12:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Reunión de amigos. Cliente prefiere vista al dique — confirmar disponibilidad en local (sábado, sin asignación sectorial).</t>
+  </si>
+  <si>
+    <t>María del mar rico</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30</t>
+  </si>
+  <si>
+    <t>1170599048</t>
+  </si>
+  <si>
+    <t>steven.ledesma01@uceva.edu.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>traen torta de cumpleaños</t>
+  </si>
+  <si>
+    <t>Nahir Figueroa</t>
+  </si>
+  <si>
+    <t>1150357273</t>
+  </si>
+  <si>
+    <t>nahir.figueroa98@gmail.com</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lorena. Lorena no paga cubierto (5+ adultos confirmados). Recibe torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emilia Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:00</t>
+  </si>
+  <si>
+    <t>+54 9 11 5151-7737</t>
+  </si>
+  <si>
+    <t>emiliaadiaz@gmail.com</t>
+  </si>
+  <si>
+    <t>10 a 12 personas.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +239,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +281,240 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>150000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,136 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexander Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1556456253</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Al_re88@hotmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita especial</t>
+  </si>
+  <si>
+    <t>Alejandro araujo</t>
+  </si>
+  <si>
+    <t>2026-06-13T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1127107738</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>Fernando Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T12:30:00</t>
+  </si>
+  <si>
+    <t>Sin asignación - Sábado</t>
+  </si>
+  <si>
+    <t>1164037680</t>
+  </si>
+  <si>
+    <t>Fernando_angel_88@hotmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 13 de Junio de 2026 a las 12:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Reunión de amigos. Cliente prefiere vista al dique — confirmar disponibilidad en local (sábado, sin asignación sectorial).</t>
+  </si>
+  <si>
+    <t>María del mar rico</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:30</t>
+  </si>
+  <si>
+    <t>1170599048</t>
+  </si>
+  <si>
+    <t>steven.ledesma01@uceva.edu.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>traen torta de cumpleaños</t>
+  </si>
+  <si>
+    <t>Nahir Figueroa</t>
+  </si>
+  <si>
+    <t>1150357273</t>
+  </si>
+  <si>
+    <t>nahir.figueroa98@gmail.com</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lorena. Lorena no paga cubierto (5+ adultos confirmados). Recibe torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emilia Diaz</t>
+  </si>
+  <si>
+    <t>2026-06-13T20:00</t>
+  </si>
+  <si>
+    <t>+54 9 11 5151-7737</t>
+  </si>
+  <si>
+    <t>emiliaadiaz@gmail.com</t>
+  </si>
+  <si>
+    <t>10 a 12 personas.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -92,7 +221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +236,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +278,240 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>150000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,124 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Emiliano León Flores</t>
+  </si>
+  <si>
+    <t>2026-06-14T22:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1164769332</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>emilianoleonflores2@hotmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente en aniversario. Cena romántica.</t>
+  </si>
+  <si>
+    <t>Osman Montaño Quezada</t>
+  </si>
+  <si>
+    <t>2026-06-14T20:30:00</t>
+  </si>
+  <si>
+    <t>A definir</t>
+  </si>
+  <si>
+    <t>1166923592</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>osman@quality.com.ar</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Cena en familia. 1 vegetariano en el grupo. Menor de 4 años. Sector a definir por el equipo al llegar.</t>
+  </si>
+  <si>
+    <t>MARIA MORETTI</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>3413407408</t>
+  </si>
+  <si>
+    <t>boutiquergazza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>señoras mayores piden cerca del buffet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CRISTINA CRIADO </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Siberia  2 MESAS 12 PERSONAS Y UNA 10P) BRINDIS
+2 liberados 
+Postre tulipa con helado de granizado 
+Congeló comida a 57.000$ por persona,bebida paga el mismo día </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soria Matheo </t>
+  </si>
+  <si>
+    <t>2026-06-14T20:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1160979137</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>MESA DIQUE</t>
   </si>
 </sst>
 </file>
@@ -92,7 +209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +224,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +266,205 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>33.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>1767000.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,142 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Christian Pensini</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>11 2552-2580</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>christianpensini@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Gloria (mamá del cliente). Aplica beneficio de cumpleaños: no paga cubierto, torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emiliano León Flores</t>
+  </si>
+  <si>
+    <t>2026-06-14T22:00:00</t>
+  </si>
+  <si>
+    <t>1164769332</t>
+  </si>
+  <si>
+    <t>emilianoleonflores2@hotmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente en aniversario. Cena romántica.</t>
+  </si>
+  <si>
+    <t>Osman Montaño Quezada</t>
+  </si>
+  <si>
+    <t>2026-06-14T20:30:00</t>
+  </si>
+  <si>
+    <t>A definir</t>
+  </si>
+  <si>
+    <t>1166923592</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>osman@quality.com.ar</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Cena en familia. 1 vegetariano en el grupo. Menor de 4 años. Sector a definir por el equipo al llegar.</t>
+  </si>
+  <si>
+    <t>MARIA MORETTI</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>3413407408</t>
+  </si>
+  <si>
+    <t>boutiquergazza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>señoras mayores piden cerca del buffet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CRISTINA CRIADO </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Siberia  2 MESAS 12 PERSONAS Y UNA 10P) BRINDIS
+2 liberados 
+Postre tulipa con helado de granizado 
+Congeló comida a 57.000$ por persona,bebida paga el mismo día </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soria Matheo </t>
+  </si>
+  <si>
+    <t>2026-06-14T20:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1160979137</t>
+  </si>
+  <si>
+    <t>MESA DIQUE</t>
   </si>
 </sst>
 </file>
@@ -92,7 +227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +242,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +284,243 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>33.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>1767000.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="57">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,145 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Christian Pensini</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>11 2552-2580</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>christianpensini@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Gloria (mamá del cliente). Aplica beneficio de cumpleaños: no paga cubierto, torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emiliano León Flores</t>
+  </si>
+  <si>
+    <t>2026-06-14T22:00:00</t>
+  </si>
+  <si>
+    <t>1164769332</t>
+  </si>
+  <si>
+    <t>emilianoleonflores2@hotmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente en aniversario. Cena romántica.</t>
+  </si>
+  <si>
+    <t>Osman Montaño Quezada</t>
+  </si>
+  <si>
+    <t>2026-06-14T20:30:00</t>
+  </si>
+  <si>
+    <t>A definir</t>
+  </si>
+  <si>
+    <t>1166923592</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>osman@quality.com.ar</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Cena en familia. 1 vegetariano en el grupo. Menor de 4 años. Sector a definir por el equipo al llegar.</t>
+  </si>
+  <si>
+    <t>MARIA MORETTI</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>3413407408</t>
+  </si>
+  <si>
+    <t>boutiquergazza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>señoras mayores piden cerca del buffet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CRISTINA CRIADO </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Siberia  2 MESAS 12 PERSONAS Y UNA 10P) BRINDIS
+2 liberados 
+Postre tulipa con helado de granizado 
+Congeló comida a 57.000$ por persona,bebida paga el mismo día </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soria Matheo </t>
+  </si>
+  <si>
+    <t>2026-06-14T20:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1160979137</t>
+  </si>
+  <si>
+    <t>MESA DIQUE</t>
   </si>
 </sst>
 </file>
@@ -92,7 +230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +245,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +287,243 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>33.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>1767000.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="61">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,157 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Emiliano Márquez</t>
+  </si>
+  <si>
+    <t>2026-06-14T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+598 9 2650524</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>marquezemiliano35@gmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Christian Pensini</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00:00</t>
+  </si>
+  <si>
+    <t>11 2552-2580</t>
+  </si>
+  <si>
+    <t>christianpensini@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Gloria (mamá del cliente). Aplica beneficio de cumpleaños: no paga cubierto, torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emiliano León Flores</t>
+  </si>
+  <si>
+    <t>2026-06-14T22:00:00</t>
+  </si>
+  <si>
+    <t>1164769332</t>
+  </si>
+  <si>
+    <t>emilianoleonflores2@hotmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente en aniversario. Cena romántica.</t>
+  </si>
+  <si>
+    <t>Osman Montaño Quezada</t>
+  </si>
+  <si>
+    <t>A definir</t>
+  </si>
+  <si>
+    <t>1166923592</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>osman@quality.com.ar</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Cena en familia. 1 vegetariano en el grupo. Menor de 4 años. Sector a definir por el equipo al llegar.</t>
+  </si>
+  <si>
+    <t>MARIA MORETTI</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>3413407408</t>
+  </si>
+  <si>
+    <t>boutiquergazza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>señoras mayores piden cerca del buffet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CRISTINA CRIADO </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Siberia  2 MESAS 12 PERSONAS Y UNA 10P) BRINDIS
+2 liberados 
+Postre tulipa con helado de granizado 
+Congeló comida a 57.000$ por persona,bebida paga el mismo día </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soria Matheo </t>
+  </si>
+  <si>
+    <t>2026-06-14T20:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1160979137</t>
+  </si>
+  <si>
+    <t>MESA DIQUE</t>
   </si>
 </sst>
 </file>
@@ -92,7 +242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +257,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +299,275 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>33.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>1767000.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="61">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,157 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Emiliano Márquez</t>
+  </si>
+  <si>
+    <t>2026-06-14T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+598 9 2650524</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>marquezemiliano35@gmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Christian Pensini</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00:00</t>
+  </si>
+  <si>
+    <t>11 2552-2580</t>
+  </si>
+  <si>
+    <t>christianpensini@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Gloria (mamá del cliente). Aplica beneficio de cumpleaños: no paga cubierto, torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emiliano León Flores</t>
+  </si>
+  <si>
+    <t>2026-06-14T22:00:00</t>
+  </si>
+  <si>
+    <t>1164769332</t>
+  </si>
+  <si>
+    <t>emilianoleonflores2@hotmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente en aniversario. Cena romántica.</t>
+  </si>
+  <si>
+    <t>Osman Montaño Quezada</t>
+  </si>
+  <si>
+    <t>A definir</t>
+  </si>
+  <si>
+    <t>1166923592</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>osman@quality.com.ar</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Cena en familia. 1 vegetariano en el grupo. Menor de 4 años. Sector a definir por el equipo al llegar.</t>
+  </si>
+  <si>
+    <t>MARIA MORETTI</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>3413407408</t>
+  </si>
+  <si>
+    <t>boutiquergazza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>señoras mayores piden cerca del buffet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CRISTINA CRIADO </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Siberia  2 MESAS 12 PERSONAS Y UNA 10P) BRINDIS
+2 liberados 
+Postre tulipa con helado de granizado 
+Congeló comida a 57.000$ por persona,bebida paga el mismo día </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soria Matheo </t>
+  </si>
+  <si>
+    <t>2026-06-14T20:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1160979137</t>
+  </si>
+  <si>
+    <t>MESA DIQUE</t>
   </si>
 </sst>
 </file>
@@ -92,7 +242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +257,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +299,275 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>33.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>1767000.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="61">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,157 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Emiliano Márquez</t>
+  </si>
+  <si>
+    <t>2026-06-14T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+598 9 2650524</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>marquezemiliano35@gmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Christian Pensini</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00:00</t>
+  </si>
+  <si>
+    <t>11 2552-2580</t>
+  </si>
+  <si>
+    <t>christianpensini@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Gloria (mamá del cliente). Aplica beneficio de cumpleaños: no paga cubierto, torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emiliano León Flores</t>
+  </si>
+  <si>
+    <t>2026-06-14T22:00:00</t>
+  </si>
+  <si>
+    <t>1164769332</t>
+  </si>
+  <si>
+    <t>emilianoleonflores2@hotmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente en aniversario. Cena romántica.</t>
+  </si>
+  <si>
+    <t>Osman Montaño Quezada</t>
+  </si>
+  <si>
+    <t>A definir</t>
+  </si>
+  <si>
+    <t>1166923592</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>osman@quality.com.ar</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Cena en familia. 1 vegetariano en el grupo. Menor de 4 años. Sector a definir por el equipo al llegar.</t>
+  </si>
+  <si>
+    <t>MARIA MORETTI</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>3413407408</t>
+  </si>
+  <si>
+    <t>boutiquergazza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>señoras mayores piden cerca del buffet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CRISTINA CRIADO </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Siberia  2 MESAS 12 PERSONAS Y UNA 10P) BRINDIS
+2 liberados 
+Postre tulipa con helado de granizado 
+Congeló comida a 57.000$ por persona,bebida paga el mismo día </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soria Matheo </t>
+  </si>
+  <si>
+    <t>2026-06-14T20:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1160979137</t>
+  </si>
+  <si>
+    <t>MESA DIQUE</t>
   </si>
 </sst>
 </file>
@@ -92,7 +242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +257,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +299,275 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>33.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>1767000.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="61">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,157 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Emiliano Márquez</t>
+  </si>
+  <si>
+    <t>2026-06-14T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+598 9 2650524</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>marquezemiliano35@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Christian Pensini</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00:00</t>
+  </si>
+  <si>
+    <t>11 2552-2580</t>
+  </si>
+  <si>
+    <t>christianpensini@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Gloria (mamá del cliente). Aplica beneficio de cumpleaños: no paga cubierto, torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emiliano León Flores</t>
+  </si>
+  <si>
+    <t>2026-06-14T22:00:00</t>
+  </si>
+  <si>
+    <t>1164769332</t>
+  </si>
+  <si>
+    <t>emilianoleonflores2@hotmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente en aniversario. Cena romántica.</t>
+  </si>
+  <si>
+    <t>Osman Montaño Quezada</t>
+  </si>
+  <si>
+    <t>A definir</t>
+  </si>
+  <si>
+    <t>1166923592</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>osman@quality.com.ar</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Cena en familia. 1 vegetariano en el grupo. Menor de 4 años. Sector a definir por el equipo al llegar.</t>
+  </si>
+  <si>
+    <t>MARIA MORETTI</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>3413407408</t>
+  </si>
+  <si>
+    <t>boutiquergazza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>señoras mayores piden cerca del buffet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CRISTINA CRIADO </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Siberia  2 MESAS 12 PERSONAS Y UNA 10P) BRINDIS
+2 liberados 
+Postre tulipa con helado de granizado 
+Congeló comida a 57.000$ por persona,bebida paga el mismo día </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soria Matheo </t>
+  </si>
+  <si>
+    <t>2026-06-14T20:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1160979137</t>
+  </si>
+  <si>
+    <t>MESA DIQUE</t>
   </si>
 </sst>
 </file>
@@ -92,7 +242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +257,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +299,275 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>33.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>1767000.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="60">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,154 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Emiliano Márquez</t>
+  </si>
+  <si>
+    <t>2026-06-14T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+598 9 2650524</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>marquezemiliano35@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Christian Pensini</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00:00</t>
+  </si>
+  <si>
+    <t>11 2552-2580</t>
+  </si>
+  <si>
+    <t>christianpensini@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Gloria (mamá del cliente). Aplica beneficio de cumpleaños: no paga cubierto, torta simbólica y champagne de cortesía.</t>
+  </si>
+  <si>
+    <t>Emiliano León Flores</t>
+  </si>
+  <si>
+    <t>2026-06-14T22:00:00</t>
+  </si>
+  <si>
+    <t>1164769332</t>
+  </si>
+  <si>
+    <t>emilianoleonflores2@hotmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 14 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Cliente en aniversario. Cena romántica.</t>
+  </si>
+  <si>
+    <t>Osman Montaño Quezada</t>
+  </si>
+  <si>
+    <t>A definir</t>
+  </si>
+  <si>
+    <t>1166923592</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>osman@quality.com.ar</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Cena en familia. 1 vegetariano en el grupo. Menor de 4 años. Sector a definir por el equipo al llegar.</t>
+  </si>
+  <si>
+    <t>MARIA MORETTI</t>
+  </si>
+  <si>
+    <t>2026-06-14T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>3413407408</t>
+  </si>
+  <si>
+    <t>boutiquergazza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>señoras mayores piden cerca del buffet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CRISTINA CRIADO </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Siberia  2 MESAS 12 PERSONAS Y UNA 10P) BRINDIS
+2 liberados 
+Postre tulipa con helado de granizado 
+Congeló comida a 57.000$ por persona,bebida paga el mismo día </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soria Matheo </t>
+  </si>
+  <si>
+    <t>2026-06-14T20:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1160979137</t>
+  </si>
+  <si>
+    <t>MESA DIQUE</t>
   </si>
 </sst>
 </file>
@@ -92,7 +239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +254,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +296,275 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>33.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="O7" t="n" s="0">
+        <v>1767000.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,74 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Adriana Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1156591319</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Zz</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Gentile Nora</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:30</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1156630969</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>DIQUE-SEÑA N608 $600.000 / CANCELO CON 283600 SEÑA 613 PAGO 1 BEBIDA X PERSONA AGUA/GASEOSA + 2 SAINT FELICIEN (1 CUMPLE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloom Alejandro </t>
+  </si>
+  <si>
+    <t>Privado</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cub x $59.000/bebida pga comensal. (4 liberados)
+En Siberia </t>
   </si>
 </sst>
 </file>
@@ -92,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +174,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +216,132 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="O2" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="O3" t="n" s="0">
+        <v>883600.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>46.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>2140000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,98 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Milagros Rodriguez Desimone</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>2216479022</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>milyrodrig33@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Lunes 15 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Milagros. Aplica beneficio: no paga cubierto, torta simbólica y copa de champagne para brindar.</t>
+  </si>
+  <si>
+    <t>Adriana Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1156591319</t>
+  </si>
+  <si>
+    <t>Zz</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Gentile Nora</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:30</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1156630969</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>DIQUE-SEÑA N608 $600.000 / CANCELO CON 283600 SEÑA 613 PAGO 1 BEBIDA X PERSONA AGUA/GASEOSA + 2 SAINT FELICIEN (1 CUMPLE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloom Alejandro </t>
+  </si>
+  <si>
+    <t>2026-06-15T12:30</t>
+  </si>
+  <si>
+    <t>Privado</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cub x $59.000/bebida pga comensal. (4 liberados)
+En Siberia </t>
   </si>
 </sst>
 </file>
@@ -92,7 +183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +198,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +240,170 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="O3" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>883600.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>47.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>2140000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,110 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Erika Barriento</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>2236699539</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>eribarriento3@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Lunes 15 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lincoln (pareja del cliente). 5 adultos + 1 niña de 5 años. Aplica beneficio de cumpleaños: Lincoln no paga cubierto, incluye torta simbólica y copa de champagne para brindar. Cliente solicita Salón Principal.</t>
+  </si>
+  <si>
+    <t>Milagros Rodriguez Desimone</t>
+  </si>
+  <si>
+    <t>2216479022</t>
+  </si>
+  <si>
+    <t>milyrodrig33@gmail.com</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Milagros. Aplica beneficio: no paga cubierto, torta simbólica y copa de champagne para brindar.</t>
+  </si>
+  <si>
+    <t>Adriana Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1156591319</t>
+  </si>
+  <si>
+    <t>Zz</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Gentile Nora</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:30</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1156630969</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>DIQUE-SEÑA N608 $600.000 / CANCELO CON 283600 SEÑA 613 PAGO 1 BEBIDA X PERSONA AGUA/GASEOSA + 2 SAINT FELICIEN (1 CUMPLE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloom Alejandro </t>
+  </si>
+  <si>
+    <t>2026-06-15T12:30</t>
+  </si>
+  <si>
+    <t>Privado</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cub x $59.000/bebida pga comensal. (4 liberados)
+En Siberia </t>
   </si>
 </sst>
 </file>
@@ -92,7 +195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +210,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +252,208 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>883600.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>47.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>2537000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,113 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Erika Barriento</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>2236699539</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>eribarriento3@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Lunes 15 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lincoln (pareja del cliente). 5 adultos + 1 niña de 5 años. Aplica beneficio de cumpleaños: Lincoln no paga cubierto, incluye torta simbólica y copa de champagne para brindar. Cliente solicita Salón Principal.</t>
+  </si>
+  <si>
+    <t>Milagros Rodriguez Desimone</t>
+  </si>
+  <si>
+    <t>2216479022</t>
+  </si>
+  <si>
+    <t>milyrodrig33@gmail.com</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Milagros. Aplica beneficio: no paga cubierto, torta simbólica y copa de champagne para brindar.</t>
+  </si>
+  <si>
+    <t>Adriana Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1156591319</t>
+  </si>
+  <si>
+    <t>Zz</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Gentile Nora</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:30</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1156630969</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>DIQUE-SEÑA N608 $600.000 / CANCELO CON 283600 SEÑA 613 PAGO 1 BEBIDA X PERSONA AGUA/GASEOSA + 2 SAINT FELICIEN (1 CUMPLE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloom Alejandro </t>
+  </si>
+  <si>
+    <t>2026-06-15T12:30</t>
+  </si>
+  <si>
+    <t>Privado</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cub x $59.000/bebida pga comensal. (4 liberados)
+En Siberia </t>
   </si>
 </sst>
 </file>
@@ -92,7 +198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +213,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +255,208 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>883600.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>47.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>2537000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="47">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,113 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Erika Barriento</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>2236699539</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>eribarriento3@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Lunes 15 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lincoln (pareja del cliente). 5 adultos + 1 niña de 5 años. Aplica beneficio de cumpleaños: Lincoln no paga cubierto, incluye torta simbólica y copa de champagne para brindar. Cliente solicita Salón Principal.</t>
+  </si>
+  <si>
+    <t>Milagros Rodriguez Desimone</t>
+  </si>
+  <si>
+    <t>2216479022</t>
+  </si>
+  <si>
+    <t>milyrodrig33@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Milagros. Aplica beneficio: no paga cubierto, torta simbólica y copa de champagne para brindar.</t>
+  </si>
+  <si>
+    <t>Adriana Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1156591319</t>
+  </si>
+  <si>
+    <t>Zz</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Gentile Nora</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:30</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1156630969</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>DIQUE-SEÑA N608 $600.000 / CANCELO CON 283600 SEÑA 613 PAGO 1 BEBIDA X PERSONA AGUA/GASEOSA + 2 SAINT FELICIEN (1 CUMPLE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloom Alejandro </t>
+  </si>
+  <si>
+    <t>2026-06-15T12:30</t>
+  </si>
+  <si>
+    <t>Privado</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cub x $59.000/bebida pga comensal. (4 liberados)
+En Siberia </t>
   </si>
 </sst>
 </file>
@@ -92,7 +198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +213,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +255,208 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>883600.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>47.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>2537000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,110 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Erika Barriento</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>2236699539</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>eribarriento3@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Lunes 15 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Lincoln (pareja del cliente). 5 adultos + 1 niña de 5 años. Aplica beneficio de cumpleaños: Lincoln no paga cubierto, incluye torta simbólica y copa de champagne para brindar. Cliente solicita Salón Principal.</t>
+  </si>
+  <si>
+    <t>Milagros Rodriguez Desimone</t>
+  </si>
+  <si>
+    <t>2216479022</t>
+  </si>
+  <si>
+    <t>milyrodrig33@gmail.com</t>
+  </si>
+  <si>
+    <t>Cumpleaños de Milagros. Aplica beneficio: no paga cubierto, torta simbólica y copa de champagne para brindar.</t>
+  </si>
+  <si>
+    <t>Adriana Rodriguez</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1156591319</t>
+  </si>
+  <si>
+    <t>Zz</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Gentile Nora</t>
+  </si>
+  <si>
+    <t>2026-06-15T13:30</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1156630969</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>DIQUE-SEÑA N608 $600.000 / CANCELO CON 283600 SEÑA 613 PAGO 1 BEBIDA X PERSONA AGUA/GASEOSA + 2 SAINT FELICIEN (1 CUMPLE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloom Alejandro </t>
+  </si>
+  <si>
+    <t>2026-06-15T12:30</t>
+  </si>
+  <si>
+    <t>Privado</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cub x $59.000/bebida pga comensal. (4 liberados)
+En Siberia </t>
   </si>
 </sst>
 </file>
@@ -92,7 +195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +210,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +252,208 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="O4" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="O5" t="n" s="0">
+        <v>883600.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>47.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="O6" t="n" s="0">
+        <v>2537000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,15 +12,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>nombre y apellido</t>
-  </si>
-  <si>
-    <t>mail cliente</t>
-  </si>
-  <si>
-    <t>telefono cliente</t>
   </si>
   <si>
     <t>fecha y hora reserva</t>
@@ -32,10 +26,16 @@
     <t>ubicacion</t>
   </si>
   <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
     <t>vegetariano</t>
   </si>
   <si>
     <t>diabetico</t>
+  </si>
+  <si>
+    <t>mail cliente</t>
   </si>
   <si>
     <t>mesa</t>
@@ -47,7 +47,16 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
   </si>
 </sst>
 </file>
@@ -92,7 +101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +116,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +158,15 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,9 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>nombre y apellido</t>
+  </si>
+  <si>
+    <t>mail cliente</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
   </si>
   <si>
     <t>fecha y hora reserva</t>
@@ -26,16 +32,10 @@
     <t>ubicacion</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
     <t>vegetariano</t>
   </si>
   <si>
     <t>diabetico</t>
-  </si>
-  <si>
-    <t>mail cliente</t>
   </si>
   <si>
     <t>mesa</t>
@@ -47,16 +47,7 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>ocasion_especial</t>
-  </si>
-  <si>
-    <t>observaciones</t>
-  </si>
-  <si>
-    <t>tiene_sena</t>
-  </si>
-  <si>
-    <t>monto_sena</t>
+    <t>sucursal</t>
   </si>
 </sst>
 </file>
@@ -101,7 +92,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -116,9 +107,6 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
-    <col min="13" max="13" width="22.0" customWidth="true"/>
-    <col min="14" max="14" width="22.0" customWidth="true"/>
-    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -158,15 +146,6 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="M1" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>14</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,43 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>ALVARO POSADAS</t>
+  </si>
+  <si>
+    <t>2026-06-16T21:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1566518138</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alvarposada@gmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>vista a la tv</t>
   </si>
 </sst>
 </file>
@@ -92,7 +128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +143,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +185,53 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,9 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>nombre y apellido</t>
+  </si>
+  <si>
+    <t>mail cliente</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
   </si>
   <si>
     <t>fecha y hora reserva</t>
@@ -26,16 +32,10 @@
     <t>ubicacion</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
     <t>vegetariano</t>
   </si>
   <si>
     <t>diabetico</t>
-  </si>
-  <si>
-    <t>mail cliente</t>
   </si>
   <si>
     <t>mesa</t>
@@ -47,43 +47,7 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>ocasion_especial</t>
-  </si>
-  <si>
-    <t>observaciones</t>
-  </si>
-  <si>
-    <t>tiene_sena</t>
-  </si>
-  <si>
-    <t>monto_sena</t>
-  </si>
-  <si>
-    <t>ALVARO POSADAS</t>
-  </si>
-  <si>
-    <t>2026-06-16T21:00</t>
-  </si>
-  <si>
-    <t>Salón</t>
-  </si>
-  <si>
-    <t>1566518138</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>alvarposada@gmail.com</t>
-  </si>
-  <si>
-    <t>M1</t>
-  </si>
-  <si>
-    <t>CONFIRMADA</t>
-  </si>
-  <si>
-    <t>vista a la tv</t>
+    <t>sucursal</t>
   </si>
 </sst>
 </file>
@@ -128,7 +92,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -143,9 +107,6 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
-    <col min="13" max="13" width="22.0" customWidth="true"/>
-    <col min="14" max="14" width="22.0" customWidth="true"/>
-    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -185,53 +146,6 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="M1" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="N2" t="s" s="0">
-        <v>19</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,43 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>ALVARO POSADAS</t>
+  </si>
+  <si>
+    <t>2026-06-16T21:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1566518138</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alvarposada@gmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>vista a la tv</t>
   </si>
 </sst>
 </file>
@@ -92,7 +128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +143,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +185,53 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,9 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>nombre y apellido</t>
+  </si>
+  <si>
+    <t>mail cliente</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
   </si>
   <si>
     <t>fecha y hora reserva</t>
@@ -26,16 +32,10 @@
     <t>ubicacion</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
     <t>vegetariano</t>
   </si>
   <si>
     <t>diabetico</t>
-  </si>
-  <si>
-    <t>mail cliente</t>
   </si>
   <si>
     <t>mesa</t>
@@ -47,43 +47,7 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>ocasion_especial</t>
-  </si>
-  <si>
-    <t>observaciones</t>
-  </si>
-  <si>
-    <t>tiene_sena</t>
-  </si>
-  <si>
-    <t>monto_sena</t>
-  </si>
-  <si>
-    <t>ALVARO POSADAS</t>
-  </si>
-  <si>
-    <t>2026-06-16T21:00</t>
-  </si>
-  <si>
-    <t>Salón</t>
-  </si>
-  <si>
-    <t>1566518138</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>alvarposada@gmail.com</t>
-  </si>
-  <si>
-    <t>M1</t>
-  </si>
-  <si>
-    <t>TERMINADA</t>
-  </si>
-  <si>
-    <t>vista a la tv</t>
+    <t>sucursal</t>
   </si>
 </sst>
 </file>
@@ -128,7 +92,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -143,9 +107,6 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
-    <col min="13" max="13" width="22.0" customWidth="true"/>
-    <col min="14" max="14" width="22.0" customWidth="true"/>
-    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -185,53 +146,6 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="M1" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="N2" t="s" s="0">
-        <v>19</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,80 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel </t>
+  </si>
+  <si>
+    <t>2026-06-17T13:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>+3519997246100</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Manuelmarques@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dique 
+Mesa 132 </t>
+  </si>
+  <si>
+    <t>JUAN MOSCOSO</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00</t>
+  </si>
+  <si>
+    <t>+54 9 3424 06-0007</t>
+  </si>
+  <si>
+    <t>nachorisso9@gmail.com</t>
+  </si>
+  <si>
+    <t>vista al rio</t>
+  </si>
+  <si>
+    <t>Yair Samudio</t>
+  </si>
+  <si>
+    <t>2026-06-17T20:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>11 36785564</t>
+  </si>
+  <si>
+    <t>yairsamudio06@gmail.com</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Juntada con amigos. Promo Miércoles y Jueves (bebida incluida).</t>
   </si>
 </sst>
 </file>
@@ -92,7 +165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +180,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +222,123 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,104 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexia Fernanda Portal</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1156529830</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>fernanda.alexia.portal@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Aniversario. Cliente solicita decoración especial. Promo Cena Miércoles y Jueves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel </t>
+  </si>
+  <si>
+    <t>2026-06-17T13:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>+3519997246100</t>
+  </si>
+  <si>
+    <t>Manuelmarques@gmail.com</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dique 
+Mesa 132 </t>
+  </si>
+  <si>
+    <t>JUAN MOSCOSO</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00</t>
+  </si>
+  <si>
+    <t>+54 9 3424 06-0007</t>
+  </si>
+  <si>
+    <t>nachorisso9@gmail.com</t>
+  </si>
+  <si>
+    <t>vista al rio</t>
+  </si>
+  <si>
+    <t>Yair Samudio</t>
+  </si>
+  <si>
+    <t>2026-06-17T20:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>11 36785564</t>
+  </si>
+  <si>
+    <t>yairsamudio06@gmail.com</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Juntada con amigos. Promo Miércoles y Jueves (bebida incluida).</t>
   </si>
 </sst>
 </file>
@@ -92,7 +189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +204,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +246,161 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,107 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexia Fernanda Portal</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1156529830</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>fernanda.alexia.portal@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Aniversario. Cliente solicita decoración especial. Promo Cena Miércoles y Jueves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel </t>
+  </si>
+  <si>
+    <t>2026-06-17T13:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>+3519997246100</t>
+  </si>
+  <si>
+    <t>Manuelmarques@gmail.com</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dique 
+Mesa 132 </t>
+  </si>
+  <si>
+    <t>JUAN MOSCOSO</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00</t>
+  </si>
+  <si>
+    <t>+54 9 3424 06-0007</t>
+  </si>
+  <si>
+    <t>nachorisso9@gmail.com</t>
+  </si>
+  <si>
+    <t>vista al rio</t>
+  </si>
+  <si>
+    <t>Yair Samudio</t>
+  </si>
+  <si>
+    <t>2026-06-17T20:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>11 36785564</t>
+  </si>
+  <si>
+    <t>yairsamudio06@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Juntada con amigos. Promo Miércoles y Jueves (bebida incluida).</t>
   </si>
 </sst>
 </file>
@@ -92,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +207,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +249,161 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,107 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alexia Fernanda Portal</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1156529830</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>fernanda.alexia.portal@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Aniversario. Cliente solicita decoración especial. Promo Cena Miércoles y Jueves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel </t>
+  </si>
+  <si>
+    <t>2026-06-17T13:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>+3519997246100</t>
+  </si>
+  <si>
+    <t>Manuelmarques@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dique 
+Mesa 132 </t>
+  </si>
+  <si>
+    <t>JUAN MOSCOSO</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00</t>
+  </si>
+  <si>
+    <t>+54 9 3424 06-0007</t>
+  </si>
+  <si>
+    <t>nachorisso9@gmail.com</t>
+  </si>
+  <si>
+    <t>vista al rio</t>
+  </si>
+  <si>
+    <t>Yair Samudio</t>
+  </si>
+  <si>
+    <t>2026-06-17T20:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>11 36785564</t>
+  </si>
+  <si>
+    <t>yairsamudio06@gmail.com</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Juntada con amigos. Promo Miércoles y Jueves (bebida incluida).</t>
   </si>
 </sst>
 </file>
@@ -92,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +207,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +249,161 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="51">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,125 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Moreau de Justo</t>
+  </si>
+  <si>
+    <t>2026-06-17T22:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1123893443</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>mreaou@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 22:30 hs</t>
+  </si>
+  <si>
+    <t>Alexia Fernanda Portal</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1156529830</t>
+  </si>
+  <si>
+    <t>fernanda.alexia.portal@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Aniversario. Cliente solicita decoración especial. Promo Cena Miércoles y Jueves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel </t>
+  </si>
+  <si>
+    <t>2026-06-17T13:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>+3519997246100</t>
+  </si>
+  <si>
+    <t>Manuelmarques@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dique 
+Mesa 132 </t>
+  </si>
+  <si>
+    <t>JUAN MOSCOSO</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00</t>
+  </si>
+  <si>
+    <t>+54 9 3424 06-0007</t>
+  </si>
+  <si>
+    <t>nachorisso9@gmail.com</t>
+  </si>
+  <si>
+    <t>vista al rio</t>
+  </si>
+  <si>
+    <t>Yair Samudio</t>
+  </si>
+  <si>
+    <t>2026-06-17T20:00:00</t>
+  </si>
+  <si>
+    <t>11 36785564</t>
+  </si>
+  <si>
+    <t>yairsamudio06@gmail.com</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Juntada con amigos. Promo Miércoles y Jueves (bebida incluida).</t>
   </si>
 </sst>
 </file>
@@ -92,7 +210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +225,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +267,193 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,122 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Moreau de Justo</t>
+  </si>
+  <si>
+    <t>2026-06-17T22:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1123893443</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>mreaou@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 22:30 hs</t>
+  </si>
+  <si>
+    <t>Alexia Fernanda Portal</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1156529830</t>
+  </si>
+  <si>
+    <t>fernanda.alexia.portal@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Aniversario. Cliente solicita decoración especial. Promo Cena Miércoles y Jueves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel </t>
+  </si>
+  <si>
+    <t>2026-06-17T13:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>+3519997246100</t>
+  </si>
+  <si>
+    <t>Manuelmarques@gmail.com</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dique 
+Mesa 132 </t>
+  </si>
+  <si>
+    <t>JUAN MOSCOSO</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00</t>
+  </si>
+  <si>
+    <t>+54 9 3424 06-0007</t>
+  </si>
+  <si>
+    <t>nachorisso9@gmail.com</t>
+  </si>
+  <si>
+    <t>vista al rio</t>
+  </si>
+  <si>
+    <t>Yair Samudio</t>
+  </si>
+  <si>
+    <t>2026-06-17T20:00:00</t>
+  </si>
+  <si>
+    <t>11 36785564</t>
+  </si>
+  <si>
+    <t>yairsamudio06@gmail.com</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Juntada con amigos. Promo Miércoles y Jueves (bebida incluida).</t>
   </si>
 </sst>
 </file>
@@ -92,7 +207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +222,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +264,193 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>49</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="51">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,125 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Moreau de Justo</t>
+  </si>
+  <si>
+    <t>2026-06-17T22:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1123893443</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>mreaou@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 22:30 hs</t>
+  </si>
+  <si>
+    <t>PRUEBA PARA CHEQUEAR FUNCIONAMIENTO DEL BOT</t>
+  </si>
+  <si>
+    <t>Alexia Fernanda Portal</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00:00</t>
+  </si>
+  <si>
+    <t>Siberia</t>
+  </si>
+  <si>
+    <t>1156529830</t>
+  </si>
+  <si>
+    <t>fernanda.alexia.portal@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>aniversario</t>
+  </si>
+  <si>
+    <t>Aniversario. Cliente solicita decoración especial. Promo Cena Miércoles y Jueves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel </t>
+  </si>
+  <si>
+    <t>2026-06-17T13:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>+3519997246100</t>
+  </si>
+  <si>
+    <t>Manuelmarques@gmail.com</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dique 
+Mesa 132 </t>
+  </si>
+  <si>
+    <t>JUAN MOSCOSO</t>
+  </si>
+  <si>
+    <t>2026-06-17T21:00</t>
+  </si>
+  <si>
+    <t>+54 9 3424 06-0007</t>
+  </si>
+  <si>
+    <t>nachorisso9@gmail.com</t>
+  </si>
+  <si>
+    <t>vista al rio</t>
+  </si>
+  <si>
+    <t>Yair Samudio</t>
+  </si>
+  <si>
+    <t>2026-06-17T20:00:00</t>
+  </si>
+  <si>
+    <t>11 36785564</t>
+  </si>
+  <si>
+    <t>yairsamudio06@gmail.com</t>
+  </si>
+  <si>
+    <t>Miércoles 17 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Juntada con amigos. Promo Miércoles y Jueves (bebida incluida).</t>
   </si>
 </sst>
 </file>
@@ -92,7 +210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +225,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +267,196 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,43 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alicia Brasas</t>
+  </si>
+  <si>
+    <t>2026-06-18T22:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1122668899</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alimaderobrasas@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 22:30 hs</t>
+  </si>
+  <si>
+    <t>RESERVA DE PRUEBA PARA VERIFICAR EL FUNCIONAMIENTO DEL BOT</t>
   </si>
 </sst>
 </file>
@@ -92,7 +128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +143,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +185,50 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,9 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>nombre y apellido</t>
+  </si>
+  <si>
+    <t>mail cliente</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
   </si>
   <si>
     <t>fecha y hora reserva</t>
@@ -26,16 +32,10 @@
     <t>ubicacion</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
     <t>vegetariano</t>
   </si>
   <si>
     <t>diabetico</t>
-  </si>
-  <si>
-    <t>mail cliente</t>
   </si>
   <si>
     <t>mesa</t>
@@ -47,43 +47,7 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>ocasion_especial</t>
-  </si>
-  <si>
-    <t>observaciones</t>
-  </si>
-  <si>
-    <t>tiene_sena</t>
-  </si>
-  <si>
-    <t>monto_sena</t>
-  </si>
-  <si>
-    <t>Alicia Brasas</t>
-  </si>
-  <si>
-    <t>2026-06-18T22:30:00</t>
-  </si>
-  <si>
-    <t>Salón Principal</t>
-  </si>
-  <si>
-    <t>1122668899</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>alimaderobrasas@gmail.com</t>
-  </si>
-  <si>
-    <t>CANCELADA</t>
-  </si>
-  <si>
-    <t>Jueves 18 de Junio de 2026 a las 22:30 hs</t>
-  </si>
-  <si>
-    <t>RESERVA DE PRUEBA PARA VERIFICAR EL FUNCIONAMIENTO DEL BOT</t>
+    <t>sucursal</t>
   </si>
 </sst>
 </file>
@@ -128,7 +92,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -143,9 +107,6 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
-    <col min="13" max="13" width="22.0" customWidth="true"/>
-    <col min="14" max="14" width="22.0" customWidth="true"/>
-    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -185,50 +146,6 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="M1" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>23</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,61 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-18T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1131808365</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>marceloperfetti@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Alicia Brasas</t>
+  </si>
+  <si>
+    <t>2026-06-18T22:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1122668899</t>
+  </si>
+  <si>
+    <t>alimaderobrasas@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 22:30 hs</t>
+  </si>
+  <si>
+    <t>RESERVA DE PRUEBA PARA VERIFICAR EL FUNCIONAMIENTO DEL BOT</t>
   </si>
 </sst>
 </file>
@@ -92,7 +146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +161,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +203,82 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,85 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Carlos Ramirez</t>
+  </si>
+  <si>
+    <t>2026-06-18T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin preferencia</t>
+  </si>
+  <si>
+    <t>1170982053</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>carlos.ramirez11041@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la pareja del cliente. Sin restricciones alimentarias. Pueden traer torta de afuera sin cargo de corte.</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-18T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1131808365</t>
+  </si>
+  <si>
+    <t>marceloperfetti@gmail.com</t>
+  </si>
+  <si>
+    <t>Alicia Brasas</t>
+  </si>
+  <si>
+    <t>2026-06-18T22:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1122668899</t>
+  </si>
+  <si>
+    <t>alimaderobrasas@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 22:30 hs</t>
+  </si>
+  <si>
+    <t>RESERVA DE PRUEBA PARA VERIFICAR EL FUNCIONAMIENTO DEL BOT</t>
   </si>
 </sst>
 </file>
@@ -92,7 +170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +185,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +227,120 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,106 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Ana Paula</t>
+  </si>
+  <si>
+    <t>2026-06-18T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>88992230355</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>paulafb25@hotmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Sin ocasión especial. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Carlos Ramirez</t>
+  </si>
+  <si>
+    <t>2026-06-18T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin preferencia</t>
+  </si>
+  <si>
+    <t>1170982053</t>
+  </si>
+  <si>
+    <t>carlos.ramirez11041@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la pareja del cliente. Sin restricciones alimentarias. Pueden traer torta de afuera sin cargo de corte.</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-18T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1131808365</t>
+  </si>
+  <si>
+    <t>marceloperfetti@gmail.com</t>
+  </si>
+  <si>
+    <t>Alicia Brasas</t>
+  </si>
+  <si>
+    <t>2026-06-18T22:30:00</t>
+  </si>
+  <si>
+    <t>1122668899</t>
+  </si>
+  <si>
+    <t>alimaderobrasas@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 22:30 hs</t>
+  </si>
+  <si>
+    <t>RESERVA DE PRUEBA PARA VERIFICAR EL FUNCIONAMIENTO DEL BOT</t>
   </si>
 </sst>
 </file>
@@ -92,7 +191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +206,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +248,155 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,109 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Ana Paula</t>
+  </si>
+  <si>
+    <t>2026-06-18T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>88992230355</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>paulafb25@hotmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Sin ocasión especial. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Carlos Ramirez</t>
+  </si>
+  <si>
+    <t>2026-06-18T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin preferencia</t>
+  </si>
+  <si>
+    <t>1170982053</t>
+  </si>
+  <si>
+    <t>carlos.ramirez11041@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la pareja del cliente. Sin restricciones alimentarias. Pueden traer torta de afuera sin cargo de corte.</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-18T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1131808365</t>
+  </si>
+  <si>
+    <t>marceloperfetti@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Alicia Brasas</t>
+  </si>
+  <si>
+    <t>2026-06-18T22:30:00</t>
+  </si>
+  <si>
+    <t>1122668899</t>
+  </si>
+  <si>
+    <t>alimaderobrasas@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 22:30 hs</t>
+  </si>
+  <si>
+    <t>RESERVA DE PRUEBA PARA VERIFICAR EL FUNCIONAMIENTO DEL BOT</t>
   </si>
 </sst>
 </file>
@@ -92,7 +194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +209,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +251,155 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,106 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Ana Paula</t>
+  </si>
+  <si>
+    <t>2026-06-18T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>88992230355</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>paulafb25@hotmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Sin ocasión especial. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Carlos Ramirez</t>
+  </si>
+  <si>
+    <t>2026-06-18T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin preferencia</t>
+  </si>
+  <si>
+    <t>1170982053</t>
+  </si>
+  <si>
+    <t>carlos.ramirez11041@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la pareja del cliente. Sin restricciones alimentarias. Pueden traer torta de afuera sin cargo de corte.</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-18T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1131808365</t>
+  </si>
+  <si>
+    <t>marceloperfetti@gmail.com</t>
+  </si>
+  <si>
+    <t>Alicia Brasas</t>
+  </si>
+  <si>
+    <t>2026-06-18T22:30:00</t>
+  </si>
+  <si>
+    <t>1122668899</t>
+  </si>
+  <si>
+    <t>alimaderobrasas@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 22:30 hs</t>
+  </si>
+  <si>
+    <t>RESERVA DE PRUEBA PARA VERIFICAR EL FUNCIONAMIENTO DEL BOT</t>
   </si>
 </sst>
 </file>
@@ -92,7 +191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +206,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +248,155 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,103 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Ana Paula</t>
+  </si>
+  <si>
+    <t>2026-06-18T20:30:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>88992230355</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>paulafb25@hotmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>Sin ocasión especial. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Carlos Ramirez</t>
+  </si>
+  <si>
+    <t>2026-06-18T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin preferencia</t>
+  </si>
+  <si>
+    <t>1170982053</t>
+  </si>
+  <si>
+    <t>carlos.ramirez11041@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la pareja del cliente. Sin restricciones alimentarias. Pueden traer torta de afuera sin cargo de corte.</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-18T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1131808365</t>
+  </si>
+  <si>
+    <t>marceloperfetti@gmail.com</t>
+  </si>
+  <si>
+    <t>Alicia Brasas</t>
+  </si>
+  <si>
+    <t>2026-06-18T22:30:00</t>
+  </si>
+  <si>
+    <t>1122668899</t>
+  </si>
+  <si>
+    <t>alimaderobrasas@gmail.com</t>
+  </si>
+  <si>
+    <t>Jueves 18 de Junio de 2026 a las 22:30 hs</t>
+  </si>
+  <si>
+    <t>RESERVA DE PRUEBA PARA VERIFICAR EL FUNCIONAMIENTO DEL BOT</t>
   </si>
 </sst>
 </file>
@@ -92,7 +188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +203,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +245,155 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,167 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +267,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +309,307 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,179 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +279,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +321,339 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="70">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,182 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +267,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +282,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +324,339 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="77">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,203 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Luca Spinnato</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>1132608193</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Lucaspinnato1@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Festejo anticipado del Día del Padre (padre viaja el domingo). Grupo: 3 adultos + 2 chicos de 12 y 14 años (cuentan como adultos). Cliente prefiere Dique — confirmar disponibilidad en local (viernes, sin asignación desde reserva).</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +303,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +345,377 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="76">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,200 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Luca Spinnato</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>1132608193</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Lucaspinnato1@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Festejo anticipado del Día del Padre (padre viaja el domingo). Grupo: 3 adultos + 2 chicos de 12 y 14 años (cuentan como adultos). Cliente prefiere Dique — confirmar disponibilidad en local (viernes, sin asignación desde reserva).</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +300,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +342,377 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,212 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>EZEQUIEL CENA</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1134082009</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>ezequiel.g.cena@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Luca Spinnato</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>1132608193</t>
+  </si>
+  <si>
+    <t>Lucaspinnato1@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Festejo anticipado del Día del Padre (padre viaja el domingo). Grupo: 3 adultos + 2 chicos de 12 y 14 años (cuentan como adultos). Cliente prefiere Dique — confirmar disponibilidad en local (viernes, sin asignación desde reserva).</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +312,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +354,412 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L12" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="86">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,230 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Javier Ahumada</t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+56998375288</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>javi7antonio@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita romántica. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>EZEQUIEL CENA</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1134082009</t>
+  </si>
+  <si>
+    <t>ezequiel.g.cena@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Luca Spinnato</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>1132608193</t>
+  </si>
+  <si>
+    <t>Lucaspinnato1@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Festejo anticipado del Día del Padre (padre viaja el domingo). Grupo: 3 adultos + 2 chicos de 12 y 14 años (cuentan como adultos). Cliente prefiere Dique — confirmar disponibilidad en local (viernes, sin asignación desde reserva).</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +330,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +372,450 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L13" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,248 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alvin Gimao</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:10:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+1 332-217-6453</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alvinjgimao@icloud.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:10 hs</t>
+  </si>
+  <si>
+    <t>Javier Ahumada</t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00:00</t>
+  </si>
+  <si>
+    <t>+56998375288</t>
+  </si>
+  <si>
+    <t>javi7antonio@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita romántica. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>EZEQUIEL CENA</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1134082009</t>
+  </si>
+  <si>
+    <t>ezequiel.g.cena@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Luca Spinnato</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>1132608193</t>
+  </si>
+  <si>
+    <t>Lucaspinnato1@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Festejo anticipado del Día del Padre (padre viaja el domingo). Grupo: 3 adultos + 2 chicos de 12 y 14 años (cuentan como adultos). Cliente prefiere Dique — confirmar disponibilidad en local (viernes, sin asignación desde reserva).</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +348,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +390,482 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="K12" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="L12" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L14" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="M14" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="89">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,239 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alvin Gimao</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:10:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+1 332-217-6453</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alvinjgimao@icloud.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:10 hs</t>
+  </si>
+  <si>
+    <t>Javier Ahumada</t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00:00</t>
+  </si>
+  <si>
+    <t>+56998375288</t>
+  </si>
+  <si>
+    <t>javi7antonio@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita romántica. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>EZEQUIEL CENA</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1134082009</t>
+  </si>
+  <si>
+    <t>ezequiel.g.cena@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Luca Spinnato</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>1132608193</t>
+  </si>
+  <si>
+    <t>Lucaspinnato1@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Festejo anticipado del Día del Padre (padre viaja el domingo). Grupo: 3 adultos + 2 chicos de 12 y 14 años (cuentan como adultos). Cliente prefiere Dique — confirmar disponibilidad en local (viernes, sin asignación desde reserva).</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +339,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +381,450 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="K11" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L13" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="89">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,239 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alvin Gimao</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:10:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+1 332-217-6453</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alvinjgimao@icloud.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:10 hs</t>
+  </si>
+  <si>
+    <t>Javier Ahumada</t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00:00</t>
+  </si>
+  <si>
+    <t>+56998375288</t>
+  </si>
+  <si>
+    <t>javi7antonio@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita romántica. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>EZEQUIEL CENA</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1134082009</t>
+  </si>
+  <si>
+    <t>ezequiel.g.cena@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Luca Spinnato</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>1132608193</t>
+  </si>
+  <si>
+    <t>Lucaspinnato1@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Festejo anticipado del Día del Padre (padre viaja el domingo). Grupo: 3 adultos + 2 chicos de 12 y 14 años (cuentan como adultos). Cliente prefiere Dique — confirmar disponibilidad en local (viernes, sin asignación desde reserva).</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +339,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +381,450 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="K11" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L13" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="89">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,239 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alvin Gimao</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:10:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+1 332-217-6453</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alvinjgimao@icloud.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:10 hs</t>
+  </si>
+  <si>
+    <t>Javier Ahumada</t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00:00</t>
+  </si>
+  <si>
+    <t>+56998375288</t>
+  </si>
+  <si>
+    <t>javi7antonio@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita romántica. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>EZEQUIEL CENA</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1134082009</t>
+  </si>
+  <si>
+    <t>ezequiel.g.cena@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Luca Spinnato</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>1132608193</t>
+  </si>
+  <si>
+    <t>Lucaspinnato1@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Festejo anticipado del Día del Padre (padre viaja el domingo). Grupo: 3 adultos + 2 chicos de 12 y 14 años (cuentan como adultos). Cliente prefiere Dique — confirmar disponibilidad en local (viernes, sin asignación desde reserva).</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +339,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +381,450 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="K11" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L13" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="89">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,239 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alvin Gimao</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:10:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+1 332-217-6453</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alvinjgimao@icloud.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:10 hs</t>
+  </si>
+  <si>
+    <t>Javier Ahumada</t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00:00</t>
+  </si>
+  <si>
+    <t>+56998375288</t>
+  </si>
+  <si>
+    <t>javi7antonio@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita romántica. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>EZEQUIEL CENA</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1134082009</t>
+  </si>
+  <si>
+    <t>ezequiel.g.cena@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Luca Spinnato</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>1132608193</t>
+  </si>
+  <si>
+    <t>Lucaspinnato1@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Festejo anticipado del Día del Padre (padre viaja el domingo). Grupo: 3 adultos + 2 chicos de 12 y 14 años (cuentan como adultos). Cliente prefiere Dique — confirmar disponibilidad en local (viernes, sin asignación desde reserva).</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +324,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +339,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +381,450 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="K11" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L13" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="88">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,236 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alvin Gimao</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:10:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>+1 332-217-6453</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alvinjgimao@icloud.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:10 hs</t>
+  </si>
+  <si>
+    <t>Javier Ahumada</t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00:00</t>
+  </si>
+  <si>
+    <t>+56998375288</t>
+  </si>
+  <si>
+    <t>javi7antonio@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 22:00 hs</t>
+  </si>
+  <si>
+    <t>cita</t>
+  </si>
+  <si>
+    <t>Cita romántica. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>EZEQUIEL CENA</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1134082009</t>
+  </si>
+  <si>
+    <t>ezequiel.g.cena@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Luca Spinnato</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:30:00</t>
+  </si>
+  <si>
+    <t>Dique</t>
+  </si>
+  <si>
+    <t>1132608193</t>
+  </si>
+  <si>
+    <t>Lucaspinnato1@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 20:30 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Festejo anticipado del Día del Padre (padre viaja el domingo). Grupo: 3 adultos + 2 chicos de 12 y 14 años (cuentan como adultos). Cliente prefiere Dique — confirmar disponibilidad en local (viernes, sin asignación desde reserva).</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>1122723713</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Magali Vazquez</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:00:00</t>
+  </si>
+  <si>
+    <t>A definir en el local</t>
+  </si>
+  <si>
+    <t>1167827998</t>
+  </si>
+  <si>
+    <t>magaliagustina19@hotmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños del grupo.</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>2026-06-19T20:00</t>
+  </si>
+  <si>
+    <t>Patio</t>
+  </si>
+  <si>
+    <t>DIQUE</t>
+  </si>
+  <si>
+    <t>Franco Moroy</t>
+  </si>
+  <si>
+    <t>2026-06-19T21:30:00</t>
+  </si>
+  <si>
+    <t>+598 99439167</t>
+  </si>
+  <si>
+    <t>fmoroyvaz27@gmail.com</t>
+  </si>
+  <si>
+    <t>Viernes 19 de Junio de 2026 a las 21:30 hs</t>
+  </si>
+  <si>
+    <t>Cena en pareja</t>
+  </si>
+  <si>
+    <t>Martinez Claudio</t>
+  </si>
+  <si>
+    <t>1141994902</t>
+  </si>
+  <si>
+    <t>claudiomartinez@live.com.ar</t>
+  </si>
+  <si>
+    <t>negocios</t>
+  </si>
+  <si>
+    <t>Cena de negocios. Cliente prefiere Dique.</t>
+  </si>
+  <si>
+    <t>Angeles Tamara González</t>
+  </si>
+  <si>
+    <t>2026-06-19T19:00:00</t>
+  </si>
+  <si>
+    <t>1176071053</t>
+  </si>
+  <si>
+    <t>stellaheine5@gmail.com</t>
+  </si>
+  <si>
+    <t>Jueves 19 de Junio de 2026 a las 19:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la clienta.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novoriente </t>
+  </si>
+  <si>
+    <t>2026-06-19T12:00</t>
+  </si>
+  <si>
+    <t>1153364142</t>
+  </si>
+  <si>
+    <t>Juanmacolinafitzroy@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son 27 pagos +2 liberados
+47.000$ con 1 agua o gaseosa incluida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian Javier </t>
+  </si>
+  <si>
+    <t>2026-06-19T22:00</t>
+  </si>
+  <si>
+    <t>1166233342</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIQUE-VISTA AL RIO </t>
   </si>
 </sst>
 </file>
@@ -92,7 +321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +336,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +378,450 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="K11" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="L11" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>29.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L13" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="52">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,128 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Ángel Manuel Cerrlano</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>11-6041-6245</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>amc170723@gamol.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Sin restricciones alimentarias ni ocasión especial.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
   </si>
 </sst>
 </file>
@@ -92,7 +213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +228,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +270,225 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="52">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,128 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Ángel Manuel Cerrlano</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>11-6041-6245</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>amc170723@gamol.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Sin restricciones alimentarias ni ocasión especial.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
   </si>
 </sst>
 </file>
@@ -92,7 +213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +228,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +270,225 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,116 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
   </si>
 </sst>
 </file>
@@ -92,7 +201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +216,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +258,190 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="54">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,134 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Dayhana Dávalos</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1140431294</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Jazzmindavalos9@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la hermana (28 años). 7 adultos + 2 menores (6 y 5 años) + 1 niño 2 años sin cargo + 1 bebé 5 meses sin cargo. Beneficio cumpleaños aplica (cumpleañera no paga cubierto). Cliente prefiere Salón Principal.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>otra</t>
   </si>
 </sst>
 </file>
@@ -92,7 +219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +234,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +276,228 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="58">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,147 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Eduardo Velasco</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1162902623</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>psi.eduvelasco@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t>Cena de familia
+Sin restricciones alimentarias</t>
+  </si>
+  <si>
+    <t>Dayhana Dávalos</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1140431294</t>
+  </si>
+  <si>
+    <t>Jazzmindavalos9@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la hermana (28 años). 7 adultos + 2 menores (6 y 5 años) + 1 niño 2 años sin cargo + 1 bebé 5 meses sin cargo. Beneficio cumpleaños aplica (cumpleañera no paga cubierto). Cliente prefiere Salón Principal.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -92,7 +232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +247,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +289,266 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,150 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Eduardo Velasco</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1162902623</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>psi.eduvelasco@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t>Cena de familia
+Sin restricciones alimentarias</t>
+  </si>
+  <si>
+    <t>Dayhana Dávalos</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1140431294</t>
+  </si>
+  <si>
+    <t>Jazzmindavalos9@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la hermana (28 años). 7 adultos + 2 menores (6 y 5 años) + 1 niño 2 años sin cargo + 1 bebé 5 meses sin cargo. Beneficio cumpleaños aplica (cumpleañera no paga cubierto). Cliente prefiere Salón Principal.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -92,7 +235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +250,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +292,266 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,150 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Eduardo Velasco</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1162902623</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>psi.eduvelasco@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t>Cena de familia
+Sin restricciones alimentarias</t>
+  </si>
+  <si>
+    <t>Dayhana Dávalos</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1140431294</t>
+  </si>
+  <si>
+    <t>Jazzmindavalos9@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la hermana (28 años). 7 adultos + 2 menores (6 y 5 años) + 1 niño 2 años sin cargo + 1 bebé 5 meses sin cargo. Beneficio cumpleaños aplica (cumpleañera no paga cubierto). Cliente prefiere Salón Principal.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -92,7 +235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +250,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +292,266 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="65">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,169 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-20T23:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Eduardo Velasco</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>1162902623</t>
+  </si>
+  <si>
+    <t>psi.eduvelasco@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t>Cena de familia
+Sin restricciones alimentarias</t>
+  </si>
+  <si>
+    <t>Dayhana Dávalos</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1140431294</t>
+  </si>
+  <si>
+    <t>Jazzmindavalos9@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la hermana (28 años). 7 adultos + 2 menores (6 y 5 años) + 1 niño 2 años sin cargo + 1 bebé 5 meses sin cargo. Beneficio cumpleaños aplica (cumpleañera no paga cubierto). Cliente prefiere Salón Principal.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -92,7 +254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +269,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +311,304 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="58">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,147 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Eduardo Velasco</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1162902623</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>psi.eduvelasco@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t>Cena de familia
+Sin restricciones alimentarias</t>
+  </si>
+  <si>
+    <t>Dayhana Dávalos</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1140431294</t>
+  </si>
+  <si>
+    <t>Jazzmindavalos9@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la hermana (28 años). 7 adultos + 2 menores (6 y 5 años) + 1 niño 2 años sin cargo + 1 bebé 5 meses sin cargo. Beneficio cumpleaños aplica (cumpleañera no paga cubierto). Cliente prefiere Salón Principal.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -92,7 +232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +247,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +289,266 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="63">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,162 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alysson Macedo</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>5537988088969</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alyssoneliasmacedo@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junho de 2026 às 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Aniversário do Alysson dia 18/06 - BENEFÍCIO APLICADO: aniversariante não paga couvert (grupo com 4 adultos). Família brasileira. Sem restrições alimentares.</t>
+  </si>
+  <si>
+    <t>Eduardo Velasco</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1162902623</t>
+  </si>
+  <si>
+    <t>psi.eduvelasco@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t>Cena de familia
+Sin restricciones alimentarias</t>
+  </si>
+  <si>
+    <t>Dayhana Dávalos</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:00:00</t>
+  </si>
+  <si>
+    <t>1140431294</t>
+  </si>
+  <si>
+    <t>Jazzmindavalos9@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la hermana (28 años). 7 adultos + 2 menores (6 y 5 años) + 1 niño 2 años sin cargo + 1 bebé 5 meses sin cargo. Beneficio cumpleaños aplica (cumpleañera no paga cubierto). Cliente prefiere Salón Principal.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -92,7 +247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +262,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +304,304 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="64">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,165 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alysson Macedo</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>5537988088969</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alyssoneliasmacedo@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junho de 2026 às 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Aniversário do Alysson dia 18/06 - BENEFÍCIO APLICADO: aniversariante não paga couvert (grupo com 4 adultos). Família brasileira. Sem restrições alimentares.</t>
+  </si>
+  <si>
+    <t>Eduardo Velasco</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1162902623</t>
+  </si>
+  <si>
+    <t>psi.eduvelasco@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t>Cena de familia
+Sin restricciones alimentarias</t>
+  </si>
+  <si>
+    <t>Dayhana Dávalos</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:00:00</t>
+  </si>
+  <si>
+    <t>1140431294</t>
+  </si>
+  <si>
+    <t>Jazzmindavalos9@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la hermana (28 años). 7 adultos + 2 menores (6 y 5 años) + 1 niño 2 años sin cargo + 1 bebé 5 meses sin cargo. Beneficio cumpleaños aplica (cumpleañera no paga cubierto). Cliente prefiere Salón Principal.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -92,7 +250,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +265,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +307,304 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="63">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,162 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Alysson Macedo</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>5537988088969</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>alyssoneliasmacedo@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junho de 2026 às 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Aniversário do Alysson dia 18/06 - BENEFÍCIO APLICADO: aniversariante não paga couvert (grupo com 4 adultos). Família brasileira. Sem restrições alimentares.</t>
+  </si>
+  <si>
+    <t>Eduardo Velasco</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1162902623</t>
+  </si>
+  <si>
+    <t>psi.eduvelasco@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t>Cena de familia
+Sin restricciones alimentarias</t>
+  </si>
+  <si>
+    <t>Dayhana Dávalos</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:00:00</t>
+  </si>
+  <si>
+    <t>1140431294</t>
+  </si>
+  <si>
+    <t>Jazzmindavalos9@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la hermana (28 años). 7 adultos + 2 menores (6 y 5 años) + 1 niño 2 años sin cargo + 1 bebé 5 meses sin cargo. Beneficio cumpleaños aplica (cumpleañera no paga cubierto). Cliente prefiere Salón Principal.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -92,7 +247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +262,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +304,304 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,183 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Juan José Funes</t>
+  </si>
+  <si>
+    <t>2026-06-20T23:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>2914137817</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>juanjofunes0022@gmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>SALON SILLONES</t>
+  </si>
+  <si>
+    <t>Alysson Macedo</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>5537988088969</t>
+  </si>
+  <si>
+    <t>alyssoneliasmacedo@gmail.com</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junho de 2026 às 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Aniversário do Alysson dia 18/06 - BENEFÍCIO APLICADO: aniversariante não paga couvert (grupo com 4 adultos). Família brasileira. Sem restrições alimentares.</t>
+  </si>
+  <si>
+    <t>Eduardo Velasco</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>1162902623</t>
+  </si>
+  <si>
+    <t>psi.eduvelasco@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t>Cena de familia
+Sin restricciones alimentarias</t>
+  </si>
+  <si>
+    <t>Dayhana Dávalos</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:00:00</t>
+  </si>
+  <si>
+    <t>1140431294</t>
+  </si>
+  <si>
+    <t>Jazzmindavalos9@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la hermana (28 años). 7 adultos + 2 menores (6 y 5 años) + 1 niño 2 años sin cargo + 1 bebé 5 meses sin cargo. Beneficio cumpleaños aplica (cumpleañera no paga cubierto). Cliente prefiere Salón Principal.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -92,7 +268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +283,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +325,342 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,180 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Juan José Funes</t>
+  </si>
+  <si>
+    <t>2026-06-20T23:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>2914137817</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>juanjofunes0022@gmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>SALON SILLONES</t>
+  </si>
+  <si>
+    <t>Alysson Macedo</t>
+  </si>
+  <si>
+    <t>2026-06-20T21:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>5537988088969</t>
+  </si>
+  <si>
+    <t>alyssoneliasmacedo@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junho de 2026 às 21:00 hs</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>Aniversário do Alysson dia 18/06 - BENEFÍCIO APLICADO: aniversariante não paga couvert (grupo com 4 adultos). Família brasileira. Sem restrições alimentares.</t>
+  </si>
+  <si>
+    <t>Eduardo Velasco</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:30</t>
+  </si>
+  <si>
+    <t>1162902623</t>
+  </si>
+  <si>
+    <t>psi.eduvelasco@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t>Cena de familia
+Sin restricciones alimentarias</t>
+  </si>
+  <si>
+    <t>Dayhana Dávalos</t>
+  </si>
+  <si>
+    <t>2026-06-20T20:00:00</t>
+  </si>
+  <si>
+    <t>1140431294</t>
+  </si>
+  <si>
+    <t>Jazzmindavalos9@gmail.com</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 20:00 hs</t>
+  </si>
+  <si>
+    <t>Cumpleaños de la hermana (28 años). 7 adultos + 2 menores (6 y 5 años) + 1 niño 2 años sin cargo + 1 bebé 5 meses sin cargo. Beneficio cumpleaños aplica (cumpleañera no paga cubierto). Cliente prefiere Salón Principal.</t>
+  </si>
+  <si>
+    <t>Germán Agostino</t>
+  </si>
+  <si>
+    <t>Sin asignar</t>
+  </si>
+  <si>
+    <t>1167410199</t>
+  </si>
+  <si>
+    <t>ger_119@hotmail.com.ar</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 21:00 hs</t>
+  </si>
+  <si>
+    <t>Ana Rasquin</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:15:00</t>
+  </si>
+  <si>
+    <t>098253596</t>
+  </si>
+  <si>
+    <t>ts.arasquin@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:15 hs</t>
+  </si>
+  <si>
+    <t>celebracion_grupo</t>
+  </si>
+  <si>
+    <t>Viajan desde Paysandú. Ocasión: disfrutar y celebrar. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Andres Mendez</t>
+  </si>
+  <si>
+    <t>1144136480</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>Jesús Isaías Aranda</t>
+  </si>
+  <si>
+    <t>2026-06-20T13:30:00</t>
+  </si>
+  <si>
+    <t>1161371482</t>
+  </si>
+  <si>
+    <t>isaiasaranda1974@gmail.com</t>
+  </si>
+  <si>
+    <t>Sábado 20 de Junio de 2026 a las 13:30 hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumpleaños de la esposa del cliente. Aplica beneficio de cumpleaños: torta simbólica, copa de champagne y cumpleañera no paga cubierto.  
+SE RESPETA LA PROMO CUMPLEAÑOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flores Jesus </t>
+  </si>
+  <si>
+    <t>1167319033</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -92,7 +265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +280,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +322,342 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>11.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="L7" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="K9" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L10" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="151">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,428 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +528,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +570,1210 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="I8" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O10" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O11" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O12" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O13" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="K19" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="L19" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M19" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="I20" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="I21" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M22" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="K23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="L23" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="M23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="I25" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="I29" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M29" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M30" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="I32" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="M32" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="L33" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="O33" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="156">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,443 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +543,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +585,1248 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="I8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O11" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O12" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O13" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="I15" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="K20" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="L20" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="M20" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="I21" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="I22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K24" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="L24" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="M24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="I25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="I26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="I30" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M30" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M31" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="I33" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="M34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="156">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,443 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +543,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +585,1248 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="I8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O11" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O12" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O13" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="I15" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="K20" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="L20" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="M20" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="I21" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="I22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K24" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="L24" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="M24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="I25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="I26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="I30" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M30" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M31" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="I33" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="M34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="166">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,473 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Antonio Tarantian</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>62991247</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tarantianantonio@gmail.com</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t>Susana Romero</t>
+  </si>
+  <si>
+    <t>1140852756</t>
+  </si>
+  <si>
+    <t>susanacai@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>SIN SEÑA 12:15</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +573,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +615,1324 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O13" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M15" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="I17" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="K22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="L22" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="M22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="I23" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K26" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="L26" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="I27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="I32" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O33" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="I35" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M35" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="N35" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L36" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="N36" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="O36" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="166">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,473 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Antonio Tarantian</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>62991247</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tarantianantonio@gmail.com</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t>Susana Romero</t>
+  </si>
+  <si>
+    <t>1140852756</t>
+  </si>
+  <si>
+    <t>susanacai@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>SIN SEÑA 12:15</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +573,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +615,1324 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O13" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M15" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="I17" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="K22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="L22" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="M22" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="I23" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K26" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="L26" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="I27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="I32" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O33" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="I35" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M35" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="N35" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L36" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="N36" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="O36" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="167">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,476 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Antonio Tarantian</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>62991247</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tarantianantonio@gmail.com</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t>Susana Romero</t>
+  </si>
+  <si>
+    <t>1140852756</t>
+  </si>
+  <si>
+    <t>susanacai@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>SIN SEÑA 12:15</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +576,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +618,1324 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O13" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M15" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="I17" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="K22" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="L22" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="M22" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="I23" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K26" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="L26" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="I27" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="I32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M32" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O33" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="I35" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M35" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="N35" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L36" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="N36" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O36" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="167">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,476 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Antonio Tarantian</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>62991247</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tarantianantonio@gmail.com</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t>Susana Romero</t>
+  </si>
+  <si>
+    <t>1140852756</t>
+  </si>
+  <si>
+    <t>susanacai@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>SIN SEÑA 12:15</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>confirmada</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +576,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +618,1324 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O13" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M15" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="I17" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="K22" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="L22" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="M22" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="I23" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K26" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="L26" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="I27" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="I32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M32" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O33" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="I35" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M35" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="N35" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L36" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="N36" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O36" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="166">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,473 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Antonio Tarantian</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>62991247</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tarantianantonio@gmail.com</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t>Susana Romero</t>
+  </si>
+  <si>
+    <t>1140852756</t>
+  </si>
+  <si>
+    <t>susanacai@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>SIN SEÑA 12:15</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +573,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +615,1324 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O13" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M15" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="I17" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="L22" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="M22" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="I23" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K26" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="L26" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="I27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="I32" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O33" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="I35" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="M35" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="N35" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="L36" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="N36" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O36" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="166">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,473 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>Antonio Tarantian</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>62991247</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>tarantianantonio@gmail.com</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t>Susana Romero</t>
+  </si>
+  <si>
+    <t>1140852756</t>
+  </si>
+  <si>
+    <t>susanacai@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>SIN SEÑA 12:15</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +573,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +615,1324 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="I9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O13" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M15" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="I17" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="L22" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="M22" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="I23" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="K26" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="L26" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="I27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="I32" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O33" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="I35" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="M35" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="N35" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="L36" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="N36" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="O36" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="171">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,488 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>CANDELA GOMEZ</t>
+  </si>
+  <si>
+    <t>2026-06-21T22:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1124759897</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>candelagomez357@gmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>PREFIERE EN EL SALON CERCA DE LA VENTANA</t>
+  </si>
+  <si>
+    <t>Antonio Tarantian</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>62991247</t>
+  </si>
+  <si>
+    <t>tarantianantonio@gmail.com</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t>Susana Romero</t>
+  </si>
+  <si>
+    <t>1140852756</t>
+  </si>
+  <si>
+    <t>susanacai@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>SIN SEÑA 12:15</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +588,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +630,1362 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M16" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K23" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="L23" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="M23" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="I25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="L27" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="M27" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="I29" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="I33" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O33" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M34" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N35" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O35" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="I36" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="N36" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="C37" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="J37" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L37" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="M37" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="N37" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O37" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="171">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,488 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>CANDELA GOMEZ</t>
+  </si>
+  <si>
+    <t>2026-06-21T22:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1124759897</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>candelagomez357@gmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>PREFIERE EN EL SALON CERCA DE LA VENTANA</t>
+  </si>
+  <si>
+    <t>Antonio Tarantian</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>62991247</t>
+  </si>
+  <si>
+    <t>tarantianantonio@gmail.com</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t>Susana Romero</t>
+  </si>
+  <si>
+    <t>1140852756</t>
+  </si>
+  <si>
+    <t>susanacai@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>SIN SEÑA 12:15</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +588,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +630,1362 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M16" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K23" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="L23" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="M23" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="I25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="L27" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="M27" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="I29" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="I33" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O33" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M34" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N35" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O35" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="I36" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="N36" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="C37" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="J37" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L37" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="M37" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="N37" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O37" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="171">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,488 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>CANDELA GOMEZ</t>
+  </si>
+  <si>
+    <t>2026-06-21T22:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1124759897</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>candelagomez357@gmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>PREFIERE EN EL SALON CERCA DE LA VENTANA</t>
+  </si>
+  <si>
+    <t>Antonio Tarantian</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>62991247</t>
+  </si>
+  <si>
+    <t>tarantianantonio@gmail.com</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t>Susana Romero</t>
+  </si>
+  <si>
+    <t>1140852756</t>
+  </si>
+  <si>
+    <t>susanacai@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>SIN SEÑA 12:15</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +588,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +630,1362 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M16" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K23" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="L23" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="M23" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="I25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="L27" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="M27" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="I29" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="I33" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O33" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M34" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N35" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O35" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="I36" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="N36" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="C37" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="J37" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L37" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="M37" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="N37" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O37" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/dumps/reservas-hoy.xlsx
+++ b/dumps/reservas-hoy.xlsx
@@ -12,32 +12,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="171">
   <si>
     <t>nombre y apellido</t>
   </si>
   <si>
+    <t>fecha y hora reserva</t>
+  </si>
+  <si>
+    <t>cantidad de personas</t>
+  </si>
+  <si>
+    <t>ubicacion</t>
+  </si>
+  <si>
+    <t>telefono cliente</t>
+  </si>
+  <si>
+    <t>vegetariano</t>
+  </si>
+  <si>
+    <t>diabetico</t>
+  </si>
+  <si>
     <t>mail cliente</t>
   </si>
   <si>
-    <t>telefono cliente</t>
-  </si>
-  <si>
-    <t>fecha y hora reserva</t>
-  </si>
-  <si>
-    <t>cantidad de personas</t>
-  </si>
-  <si>
-    <t>ubicacion</t>
-  </si>
-  <si>
-    <t>vegetariano</t>
-  </si>
-  <si>
-    <t>diabetico</t>
-  </si>
-  <si>
     <t>mesa</t>
   </si>
   <si>
@@ -47,7 +47,488 @@
     <t>fecha_display</t>
   </si>
   <si>
-    <t>sucursal</t>
+    <t>ocasion_especial</t>
+  </si>
+  <si>
+    <t>observaciones</t>
+  </si>
+  <si>
+    <t>tiene_sena</t>
+  </si>
+  <si>
+    <t>monto_sena</t>
+  </si>
+  <si>
+    <t>CANDELA GOMEZ</t>
+  </si>
+  <si>
+    <t>2026-06-21T22:00</t>
+  </si>
+  <si>
+    <t>Salón</t>
+  </si>
+  <si>
+    <t>1124759897</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>candelagomez357@gmail.com</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>CONFIRMADA</t>
+  </si>
+  <si>
+    <t>PREFIERE EN EL SALON CERCA DE LA VENTANA</t>
+  </si>
+  <si>
+    <t>Antonio Tarantian</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00</t>
+  </si>
+  <si>
+    <t>62991247</t>
+  </si>
+  <si>
+    <t>tarantianantonio@gmail.com</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>TERMINADA</t>
+  </si>
+  <si>
+    <t>12:15 SIN SEÑA</t>
+  </si>
+  <si>
+    <t>Susana Romero</t>
+  </si>
+  <si>
+    <t>1140852756</t>
+  </si>
+  <si>
+    <t>susanacai@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>SIN SEÑA 12:15</t>
+  </si>
+  <si>
+    <t>EDGARDO NAVIA</t>
+  </si>
+  <si>
+    <t>1170827642</t>
+  </si>
+  <si>
+    <t>navia_edgardo@hotmail.com</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Spataro </t>
+  </si>
+  <si>
+    <t>2026-06-21T12:30</t>
+  </si>
+  <si>
+    <t>2352 443788</t>
+  </si>
+  <si>
+    <t>Josespataro2005@gmail.com</t>
+  </si>
+  <si>
+    <t>SIN SEÑA</t>
+  </si>
+  <si>
+    <t>ALAN MACRI</t>
+  </si>
+  <si>
+    <t>1150504629</t>
+  </si>
+  <si>
+    <t>alanmacri37@gmail.com</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00</t>
+  </si>
+  <si>
+    <t>Terraza</t>
+  </si>
+  <si>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>Mmmmmmmm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Es cliente va sin seña
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acevedo Rosalia Veronica </t>
+  </si>
+  <si>
+    <t>1153316342</t>
+  </si>
+  <si>
+    <t>rosiacevedo3@gmail.com</t>
+  </si>
+  <si>
+    <t>otra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Martín melizza</t>
+  </si>
+  <si>
+    <t>1160421566</t>
+  </si>
+  <si>
+    <t>martin_melizza@hotmail.com</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>Emma Cabrera</t>
+  </si>
+  <si>
+    <t>1159713861</t>
+  </si>
+  <si>
+    <t>emmacarolinacabrera@gmail.com</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>IVANA CABRERA</t>
+  </si>
+  <si>
+    <t>2026-06-21T21:30</t>
+  </si>
+  <si>
+    <t>03816048109</t>
+  </si>
+  <si>
+    <t>ivanacabreraonaindia@gmail.com</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>2 MAYORES
+2 MENORES</t>
+  </si>
+  <si>
+    <t>Agostina Belen Morete</t>
+  </si>
+  <si>
+    <t>1169987647</t>
+  </si>
+  <si>
+    <t>agosmorete31@gmail.com</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>FABIANA BALCARSE</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>sEÑA EN EFECT 638</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Varel</t>
+  </si>
+  <si>
+    <t>1141562841</t>
+  </si>
+  <si>
+    <t>fervarela_80@hotmail.com</t>
+  </si>
+  <si>
+    <t>Romina Fernandez</t>
+  </si>
+  <si>
+    <t>2026-06-21T20:00</t>
+  </si>
+  <si>
+    <t>123573526</t>
+  </si>
+  <si>
+    <t>rominacarlafernandez23@gmail.com</t>
+  </si>
+  <si>
+    <t>PAGO TOTAL DE 5 PERSONAS + 1 CUMPLE CENA DOMINGO</t>
+  </si>
+  <si>
+    <t>Myriam Roldan</t>
+  </si>
+  <si>
+    <t>+5492215997968</t>
+  </si>
+  <si>
+    <t>roldanmyriam4@gmail.com</t>
+  </si>
+  <si>
+    <t>Julieta Cuevas</t>
+  </si>
+  <si>
+    <t>+5492996218113</t>
+  </si>
+  <si>
+    <t>julieta981@outlook.com</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>Federico Brazao</t>
+  </si>
+  <si>
+    <t>1132859422</t>
+  </si>
+  <si>
+    <t>federicobrazao@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL ALVAREZ </t>
+  </si>
+  <si>
+    <t>1150142235</t>
+  </si>
+  <si>
+    <t>....</t>
+  </si>
+  <si>
+    <t>Natalia Betanzo Arnoni</t>
+  </si>
+  <si>
+    <t>1138560576</t>
+  </si>
+  <si>
+    <t>natalia.noni@hotmail.com</t>
+  </si>
+  <si>
+    <t>VALERIA FERNANDEZ</t>
+  </si>
+  <si>
+    <t>11 31586710</t>
+  </si>
+  <si>
+    <t>valaylen1962@gmail.com</t>
+  </si>
+  <si>
+    <t>Silvia García</t>
+  </si>
+  <si>
+    <t>2026-06-21T13:00:00</t>
+  </si>
+  <si>
+    <t>Salón Principal</t>
+  </si>
+  <si>
+    <t>1162662282</t>
+  </si>
+  <si>
+    <t>javsil2404@hotmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 13:00 hs</t>
+  </si>
+  <si>
+    <t>Festejar el Día del Padre. Sin restricciones alimentarias. Cliente prefiere Salón Principal para más espacio y acceso cómodo a las islas.</t>
+  </si>
+  <si>
+    <t>Ramon Brites</t>
+  </si>
+  <si>
+    <t>1123396568</t>
+  </si>
+  <si>
+    <t>ramon.brites08@gmail.com</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>Franco Dipascuo</t>
+  </si>
+  <si>
+    <t>1165703201</t>
+  </si>
+  <si>
+    <t>frandipa97@hotmail.com</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Sacerdote</t>
+  </si>
+  <si>
+    <t>+5492901568809</t>
+  </si>
+  <si>
+    <t>TRANSFERENCIA DE $70.000 A CONFIRMAR ACREDITACION</t>
+  </si>
+  <si>
+    <t>Valentina Chazarreta</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:00:00</t>
+  </si>
+  <si>
+    <t>1171626960</t>
+  </si>
+  <si>
+    <t>valenchazarreta1@gmail.com</t>
+  </si>
+  <si>
+    <t>Domingo 21 de Junio de 2026 a las 12:00 hs</t>
+  </si>
+  <si>
+    <t>Día del Padre. Sin restricciones alimentarias.</t>
+  </si>
+  <si>
+    <t>Juan CRuz Salaberry</t>
+  </si>
+  <si>
+    <t>1161539775</t>
+  </si>
+  <si>
+    <t>salaberryjuancruz04@gmail.com</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>Facundo Noir</t>
+  </si>
+  <si>
+    <t>1161388958</t>
+  </si>
+  <si>
+    <t>facundo-noir@hotmail.com</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romina Vivas </t>
+  </si>
+  <si>
+    <t>1161814767</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CARLOS FRANCIA</t>
+  </si>
+  <si>
+    <t>11 6988-2627</t>
+  </si>
+  <si>
+    <t>cdfrancia@gmail.com</t>
+  </si>
+  <si>
+    <t>SOL CUEVAS</t>
+  </si>
+  <si>
+    <t>11 2455-5458</t>
+  </si>
+  <si>
+    <t>cuevas.sol@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micaela Viera </t>
+  </si>
+  <si>
+    <t>1166271652</t>
+  </si>
+  <si>
+    <t>micaelaviera066@gmail.com</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOS ADULTOS
+DOS MENORES
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miriam Sosa </t>
+  </si>
+  <si>
+    <t>1131042090</t>
+  </si>
+  <si>
+    <t>Michitasosa61@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7 adultos y 4 niños, en lo posible que sea adentro</t>
+  </si>
+  <si>
+    <t>GABRIELA OLIVERA</t>
+  </si>
+  <si>
+    <t>1125925360</t>
+  </si>
+  <si>
+    <t>neo.fabian.vega@gmail.com</t>
+  </si>
+  <si>
+    <t>Jorge Alvarez</t>
+  </si>
+  <si>
+    <t>1131153313</t>
+  </si>
+  <si>
+    <t>Cdo602@yahoo.com.ar</t>
+  </si>
+  <si>
+    <t>ENVIO LA SEÑA A OTRA CUENTA, PIDIO QUE SE LE GUARDE LA RESERVA Y DIJO QUE VA A VENIR Y QUE SI RECUPERA LA EL DINERO VA A HACER LA SEÑA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponce Tomas </t>
+  </si>
+  <si>
+    <t>2026-06-21T20:30</t>
+  </si>
+  <si>
+    <t>1141779695</t>
+  </si>
+  <si>
+    <t>thomasponce389@gmail.com</t>
+  </si>
+  <si>
+    <t>cumpleaños</t>
+  </si>
+  <si>
+    <t>SEÑA DE $180.000 POR TRANSFERENCIA A REVISAR</t>
   </si>
 </sst>
 </file>
@@ -92,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.0" customWidth="true"/>
@@ -107,6 +588,9 @@
     <col min="10" max="10" width="22.0" customWidth="true"/>
     <col min="11" max="11" width="22.0" customWidth="true"/>
     <col min="12" max="12" width="22.0" customWidth="true"/>
+    <col min="13" max="13" width="22.0" customWidth="true"/>
+    <col min="14" max="14" width="22.0" customWidth="true"/>
+    <col min="15" max="15" width="22.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -146,6 +630,1362 @@
       <c r="L1" t="s" s="0">
         <v>11</v>
       </c>
+      <c r="M1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="J4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="N4" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="N5" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N6" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="L9" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="I10" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="I11" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="I12" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="N13" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M14" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O14" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N15" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O15" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="M16" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O16" t="n" s="0">
+        <v>300000.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N17" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O17" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="I18" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N18" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O18" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N19" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O19" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N20" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>135000.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="J21" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N21" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N22" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O22" t="n" s="0">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K23" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="L23" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="M23" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="N23" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O23" t="n" s="0">
+        <v>59000.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="I24" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N24" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O24" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="I25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N25" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O25" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="J26" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M26" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="N26" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O26" t="n" s="0">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="K27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="L27" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="M27" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="N27" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O27" t="n" s="0">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="I28" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N28" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O28" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="I29" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="J29" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N29" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O29" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N30" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O30" t="n" s="0">
+        <v>295000.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>14.0</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="J31" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N31" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O31" t="n" s="0">
+        <v>150000.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N32" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O32" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="I33" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="J33" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="M33" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="N33" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O33" t="n" s="0">
+        <v>200000.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="J34" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M34" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="N34" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O34" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="J35" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="N35" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O35" t="n" s="0">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="I36" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="M36" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="N36" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="C37" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="J37" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="L37" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="M37" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="N37" t="s" s="0">
+        <v>81</v>
+      </c>
+      <c r="O37" t="n" s="0">
+        <v>180000.0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
